--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27413A2E-E713-7947-9EC1-72E3613D5124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A1519E-D652-CF44-9E5B-602AD3A4E139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="131">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -423,6 +423,15 @@
   </si>
   <si>
     <t>Buy-in amounts and placements are approximate. If you have a more accurate recollection, let me know!</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-05</t>
+  </si>
+  <si>
+    <t>Wednesday 8/5/26</t>
+  </si>
+  <si>
+    <t>Max M.</t>
   </si>
 </sst>
 </file>
@@ -1352,8 +1361,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:J8" totalsRowShown="0">
-  <autoFilter ref="A4:J8" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:J9" totalsRowShown="0">
+  <autoFilter ref="A4:J9" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1371,7 +1380,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D38" totalsRowShown="0" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D48" totalsRowShown="0" dataDxfId="16">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1801,7 +1810,7 @@
       </c>
       <c r="H8" s="44">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
@@ -1882,7 +1891,7 @@
       </c>
       <c r="H11" s="45">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
@@ -3583,8 +3592,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
     <col min="2" max="2" width="27" style="1" customWidth="1"/>
@@ -3845,6 +3854,35 @@
         <v>20</v>
       </c>
       <c r="J8" s="41"/>
+    </row>
+    <row r="9" spans="1:10" ht="24" customHeight="1">
+      <c r="A9" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="30">
+        <v>46239</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="32">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I9" s="38">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3873,8 +3911,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
@@ -3883,7 +3921,7 @@
     <col min="5" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" customHeight="1">
+    <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="61" t="s">
         <v>61</v>
       </c>
@@ -3891,7 +3929,7 @@
       <c r="C1" s="61"/>
       <c r="D1" s="61"/>
     </row>
-    <row r="2" spans="1:4" ht="21" customHeight="1">
+    <row r="2" spans="1:4" ht="24" customHeight="1">
       <c r="A2" s="63" t="s">
         <v>62</v>
       </c>
@@ -3899,7 +3937,7 @@
       <c r="C2" s="63"/>
       <c r="D2" s="63"/>
     </row>
-    <row r="3" spans="1:4" ht="21" customHeight="1">
+    <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="77" t="s">
         <v>63</v>
       </c>
@@ -3907,7 +3945,7 @@
       <c r="C3" s="77"/>
       <c r="D3" s="77"/>
     </row>
-    <row r="4" spans="1:4" ht="21" customHeight="1">
+    <row r="4" spans="1:4" ht="24" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>48</v>
       </c>
@@ -3921,7 +3959,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="21" customHeight="1">
+    <row r="5" spans="1:4" ht="24" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>49</v>
       </c>
@@ -3935,7 +3973,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="21" customHeight="1">
+    <row r="6" spans="1:4" ht="24" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>49</v>
       </c>
@@ -3949,7 +3987,7 @@
         <v>41.25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="21" customHeight="1">
+    <row r="7" spans="1:4" ht="24" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>49</v>
       </c>
@@ -3963,7 +4001,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="21" customHeight="1">
+    <row r="8" spans="1:4" ht="24" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
@@ -3977,7 +4015,7 @@
         <v>48.55</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="21" customHeight="1">
+    <row r="9" spans="1:4" ht="24" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>49</v>
       </c>
@@ -3991,7 +4029,7 @@
         <v>23.25</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="21" customHeight="1">
+    <row r="10" spans="1:4" ht="24" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>49</v>
       </c>
@@ -4005,7 +4043,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="21" customHeight="1">
+    <row r="11" spans="1:4" ht="24" customHeight="1">
       <c r="A11" s="13" t="s">
         <v>49</v>
       </c>
@@ -4019,7 +4057,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="21" customHeight="1">
+    <row r="12" spans="1:4" ht="24" customHeight="1">
       <c r="A12" s="13" t="s">
         <v>49</v>
       </c>
@@ -4033,7 +4071,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="21" customHeight="1">
+    <row r="13" spans="1:4" ht="24" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>49</v>
       </c>
@@ -4047,7 +4085,7 @@
         <v>30.05</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="21" customHeight="1">
+    <row r="14" spans="1:4" ht="24" customHeight="1">
       <c r="A14" s="13" t="s">
         <v>54</v>
       </c>
@@ -4061,7 +4099,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="21" customHeight="1">
+    <row r="15" spans="1:4" ht="24" customHeight="1">
       <c r="A15" s="13" t="s">
         <v>54</v>
       </c>
@@ -4075,7 +4113,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="21" customHeight="1">
+    <row r="16" spans="1:4" ht="24" customHeight="1">
       <c r="A16" s="13" t="s">
         <v>54</v>
       </c>
@@ -4089,7 +4127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="21" customHeight="1">
+    <row r="17" spans="1:4" ht="24" customHeight="1">
       <c r="A17" s="13" t="s">
         <v>54</v>
       </c>
@@ -4103,7 +4141,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="21" customHeight="1">
+    <row r="18" spans="1:4" ht="24" customHeight="1">
       <c r="A18" s="13" t="s">
         <v>54</v>
       </c>
@@ -4117,7 +4155,7 @@
         <v>143.9</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="21" customHeight="1">
+    <row r="19" spans="1:4" ht="24" customHeight="1">
       <c r="A19" s="13" t="s">
         <v>54</v>
       </c>
@@ -4131,7 +4169,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="21" customHeight="1">
+    <row r="20" spans="1:4" ht="24" customHeight="1">
       <c r="A20" s="13" t="s">
         <v>54</v>
       </c>
@@ -4145,7 +4183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="21" customHeight="1">
+    <row r="21" spans="1:4" ht="24" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>54</v>
       </c>
@@ -4159,7 +4197,7 @@
         <v>148.9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="21" customHeight="1">
+    <row r="22" spans="1:4" ht="24" customHeight="1">
       <c r="A22" s="13" t="s">
         <v>57</v>
       </c>
@@ -4173,7 +4211,7 @@
         <v>73.75</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="21" customHeight="1">
+    <row r="23" spans="1:4" ht="24" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>57</v>
       </c>
@@ -4187,7 +4225,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="21" customHeight="1">
+    <row r="24" spans="1:4" ht="24" customHeight="1">
       <c r="A24" s="13" t="s">
         <v>57</v>
       </c>
@@ -4201,7 +4239,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="21" customHeight="1">
+    <row r="25" spans="1:4" ht="24" customHeight="1">
       <c r="A25" s="13" t="s">
         <v>57</v>
       </c>
@@ -4215,7 +4253,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="21" customHeight="1">
+    <row r="26" spans="1:4" ht="24" customHeight="1">
       <c r="A26" s="13" t="s">
         <v>57</v>
       </c>
@@ -4229,7 +4267,7 @@
         <v>23.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="21" customHeight="1">
+    <row r="27" spans="1:4" ht="24" customHeight="1">
       <c r="A27" s="13" t="s">
         <v>57</v>
       </c>
@@ -4243,7 +4281,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="21" customHeight="1">
+    <row r="28" spans="1:4" ht="24" customHeight="1">
       <c r="A28" s="13" t="s">
         <v>57</v>
       </c>
@@ -4257,7 +4295,7 @@
         <v>30.25</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="21" customHeight="1">
+    <row r="29" spans="1:4" ht="24" customHeight="1">
       <c r="A29" s="13" t="s">
         <v>57</v>
       </c>
@@ -4271,7 +4309,7 @@
         <v>34.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="21" customHeight="1">
+    <row r="30" spans="1:4" ht="24" customHeight="1">
       <c r="A30" s="13" t="s">
         <v>57</v>
       </c>
@@ -4285,7 +4323,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="21" customHeight="1">
+    <row r="31" spans="1:4" ht="24" customHeight="1">
       <c r="A31" s="13" t="s">
         <v>59</v>
       </c>
@@ -4299,7 +4337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="21" customHeight="1">
+    <row r="32" spans="1:4" ht="24" customHeight="1">
       <c r="A32" s="13" t="s">
         <v>59</v>
       </c>
@@ -4313,7 +4351,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="21" customHeight="1">
+    <row r="33" spans="1:4" ht="24" customHeight="1">
       <c r="A33" s="13" t="s">
         <v>59</v>
       </c>
@@ -4327,7 +4365,7 @@
         <v>47.75</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="21" customHeight="1">
+    <row r="34" spans="1:4" ht="24" customHeight="1">
       <c r="A34" s="13" t="s">
         <v>59</v>
       </c>
@@ -4341,7 +4379,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="21" customHeight="1">
+    <row r="35" spans="1:4" ht="24" customHeight="1">
       <c r="A35" s="13" t="s">
         <v>59</v>
       </c>
@@ -4355,7 +4393,7 @@
         <v>24.25</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="21" customHeight="1">
+    <row r="36" spans="1:4" ht="24" customHeight="1">
       <c r="A36" s="13" t="s">
         <v>59</v>
       </c>
@@ -4369,7 +4407,7 @@
         <v>48.25</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="21" customHeight="1">
+    <row r="37" spans="1:4" ht="24" customHeight="1">
       <c r="A37" s="13" t="s">
         <v>59</v>
       </c>
@@ -4383,7 +4421,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="21" customHeight="1">
+    <row r="38" spans="1:4" ht="24" customHeight="1">
       <c r="A38" s="13" t="s">
         <v>59</v>
       </c>
@@ -4395,6 +4433,146 @@
       </c>
       <c r="D38" s="14">
         <v>73.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="24" customHeight="1">
+      <c r="A39" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="14">
+        <v>20</v>
+      </c>
+      <c r="D39" s="14">
+        <v>30.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="24" customHeight="1">
+      <c r="A40" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="14">
+        <v>20</v>
+      </c>
+      <c r="D40" s="14">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="24" customHeight="1">
+      <c r="A41" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="14">
+        <v>70</v>
+      </c>
+      <c r="D41" s="14">
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="24" customHeight="1">
+      <c r="A42" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="14">
+        <v>20</v>
+      </c>
+      <c r="D42" s="14">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="24" customHeight="1">
+      <c r="A43" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="14">
+        <v>70</v>
+      </c>
+      <c r="D43" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="24" customHeight="1">
+      <c r="A44" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="14">
+        <v>20</v>
+      </c>
+      <c r="D44" s="14">
+        <v>42.75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="24" customHeight="1">
+      <c r="A45" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="14">
+        <v>20</v>
+      </c>
+      <c r="D45" s="14">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="24" customHeight="1">
+      <c r="A46" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="14">
+        <v>40</v>
+      </c>
+      <c r="D46" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="24" customHeight="1">
+      <c r="A47" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="14">
+        <v>20</v>
+      </c>
+      <c r="D47" s="14">
+        <v>73.75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="24" customHeight="1">
+      <c r="A48" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="14">
+        <v>30</v>
+      </c>
+      <c r="D48" s="14">
+        <v>36.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A1519E-D652-CF44-9E5B-602AD3A4E139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C91DC6-396B-C74D-BBD3-59E6903BB36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="133">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -432,6 +432,12 @@
   </si>
   <si>
     <t>Max M.</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-08</t>
+  </si>
+  <si>
+    <t>Saturday 8/8/26</t>
   </si>
 </sst>
 </file>
@@ -927,6 +933,42 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -940,45 +982,9 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -986,27 +992,25 @@
   <dxfs count="28">
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
+        <b/>
+        <color rgb="FF173F32"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDECE4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
+        <b/>
+        <color rgb="FF173F32"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDECE4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1099,25 +1103,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color rgb="FF173F32"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDECE4"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color rgb="FF173F32"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDECE4"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1361,8 +1367,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:J9" totalsRowShown="0">
-  <autoFilter ref="A4:J9" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:J10" totalsRowShown="0">
+  <autoFilter ref="A4:J10" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1380,7 +1386,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D48" totalsRowShown="0" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D56" totalsRowShown="0" dataDxfId="16">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1409,7 +1415,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="AnnouncementsTable" displayName="AnnouncementsTable" ref="A4:G7" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="AnnouncementsTable" displayName="AnnouncementsTable" ref="A4:G7" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A4:G7" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Announcement ID" dataDxfId="8"/>
@@ -1629,106 +1635,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="71" t="s">
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="67" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="71" t="s">
+      <c r="A2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="67" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="72" t="s">
+      <c r="H3" s="68" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="73" t="s">
+      <c r="G5" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="73" t="s">
+      <c r="H5" s="69" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1736,22 +1742,22 @@
       <c r="A6" s="43">
         <v>1</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F6" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="71" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="44">
@@ -1763,22 +1769,22 @@
       <c r="A7" s="43">
         <v>2</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="66" t="s">
+      <c r="D7" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="66" t="s">
+      <c r="E7" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="69" t="s">
+      <c r="F7" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="73" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="45">
@@ -1790,49 +1796,49 @@
       <c r="A8" s="43">
         <v>3</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="68" t="s">
+      <c r="F8" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="71" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="44">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="43">
         <v>4</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="66" t="s">
+      <c r="D9" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="66" t="s">
+      <c r="E9" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="69" t="s">
+      <c r="F9" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="73" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="45">
@@ -1844,22 +1850,22 @@
       <c r="A10" s="43">
         <v>5</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="E10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="68" t="s">
+      <c r="F10" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="71" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="44">
@@ -1871,237 +1877,237 @@
       <c r="A11" s="43">
         <v>6</v>
       </c>
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C11" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="66" t="s">
+      <c r="E11" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="69" t="s">
+      <c r="G11" s="73" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="45">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="70" t="s">
+      <c r="B14" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="70" t="s">
+      <c r="D14" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="70" t="s">
+      <c r="E14" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="70" t="s">
+      <c r="F14" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="70" t="s">
+      <c r="G14" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="70" t="s">
+      <c r="H14" s="74" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="67" t="s">
+      <c r="A15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="67" t="s">
+      <c r="C15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="D15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="67" t="s">
+      <c r="E15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="67" t="s">
+      <c r="F15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="67" t="s">
+      <c r="G15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="67" t="s">
+      <c r="H15" s="70" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="66" t="s">
+      <c r="D16" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="66" t="s">
+      <c r="E16" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="66" t="s">
+      <c r="F16" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="66" t="s">
+      <c r="G16" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="66" t="s">
+      <c r="H16" s="72" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="67" t="s">
+      <c r="A17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="70" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="66" t="s">
+      <c r="C18" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="66" t="s">
+      <c r="D18" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="66" t="s">
+      <c r="E18" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="66" t="s">
+      <c r="F18" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="66" t="s">
+      <c r="G18" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="66" t="s">
+      <c r="H18" s="72" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="67" t="s">
+      <c r="C19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="D19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="67" t="s">
+      <c r="E19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="67" t="s">
+      <c r="F19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="67" t="s">
+      <c r="G19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="67" t="s">
+      <c r="H19" s="70" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="66" t="s">
+      <c r="A20" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="66" t="s">
+      <c r="D20" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="66" t="s">
+      <c r="E20" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="66" t="s">
+      <c r="F20" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="66" t="s">
+      <c r="G20" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="66" t="s">
+      <c r="H20" s="72" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2126,98 +2132,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="F1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="74" t="s">
+      <c r="I1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="74" t="s">
+      <c r="J1" s="64" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="75" t="s">
+      <c r="H2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="75" t="s">
+      <c r="J2" s="65" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="24" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="76" t="s">
+      <c r="I3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="76" t="s">
+      <c r="J3" s="66" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2374,7 +2380,7 @@
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G198">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="upcoming"/>
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" sqref="G5:G198" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -2410,43 +2416,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
     </row>
     <row r="2" spans="1:9" ht="31" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="1:9" ht="25" customHeight="1">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="79" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
     </row>
     <row r="4" spans="1:9" ht="34" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -3592,7 +3598,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -3608,98 +3614,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="F1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="74" t="s">
+      <c r="I1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="74" t="s">
+      <c r="J1" s="64" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="75" t="s">
+      <c r="H2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="75" t="s">
+      <c r="J2" s="65" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="24" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="76" t="s">
+      <c r="I3" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="76" t="s">
+      <c r="J3" s="66" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3881,6 +3887,35 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="I9" s="38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="24" customHeight="1">
+      <c r="A10" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="30">
+        <v>46242</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="32">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I10" s="38">
         <v>20</v>
       </c>
     </row>
@@ -3891,7 +3926,7 @@
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G199">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="upcoming"/>
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" sqref="G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -3911,7 +3946,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43" style="1" customWidth="1"/>
@@ -3922,28 +3957,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="77" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -4573,6 +4608,118 @@
       </c>
       <c r="D48" s="14">
         <v>36.75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="24" customHeight="1">
+      <c r="A49" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="14">
+        <v>20</v>
+      </c>
+      <c r="D49" s="14">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="24" customHeight="1">
+      <c r="A50" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="14">
+        <v>40</v>
+      </c>
+      <c r="D50" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="24" customHeight="1">
+      <c r="A51" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="14">
+        <v>20</v>
+      </c>
+      <c r="D51" s="14">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="24" customHeight="1">
+      <c r="A52" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="14">
+        <v>20</v>
+      </c>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="24" customHeight="1">
+      <c r="A53" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="14">
+        <v>20</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="24" customHeight="1">
+      <c r="A54" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="14">
+        <v>20</v>
+      </c>
+      <c r="D54" s="14">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="24" customHeight="1">
+      <c r="A55" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="14">
+        <v>20</v>
+      </c>
+      <c r="D55" s="14">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="24" customHeight="1">
+      <c r="A56" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="14">
+        <v>20</v>
+      </c>
+      <c r="D56" s="14">
+        <v>45.3</v>
       </c>
     </row>
   </sheetData>
@@ -4611,53 +4758,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="64" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="65" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="66" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4767,71 +4914,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="F1" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="64" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="65" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="66" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4862,7 +5009,7 @@
       <c r="A5" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="79">
+      <c r="B5" s="62">
         <v>46236</v>
       </c>
       <c r="C5" s="60" t="s">
@@ -4874,7 +5021,7 @@
       <c r="E5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F5" s="79">
+      <c r="F5" s="62">
         <v>46305</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -4885,7 +5032,7 @@
       <c r="A6" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="80">
+      <c r="B6" s="63">
         <v>46236</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -4894,7 +5041,7 @@
       <c r="D6" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="78" t="s">
+      <c r="E6" s="61" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4902,7 +5049,7 @@
       <c r="A7" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="80">
+      <c r="B7" s="63">
         <v>46236</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -4911,7 +5058,7 @@
       <c r="D7" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="78" t="s">
+      <c r="E7" s="61" t="s">
         <v>37</v>
       </c>
     </row>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C91DC6-396B-C74D-BBD3-59E6903BB36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2907AA-17D6-D743-9D7A-6696F8FFDA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="620" windowWidth="30240" windowHeight="17800" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="135">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -407,9 +407,6 @@
     <t>Save the Date: October 10th High-Stakes Tournamet</t>
   </si>
   <si>
-    <t>I will be hosting a $50 buy-in tournament on October 10th at 6:30 PM. Stay tuned for a formal invite in the next few weeks, but put it on your calendar now! If we can get 20 players, the total prize pool will be $1,000!</t>
-  </si>
-  <si>
     <t>October 2026 High-Stakes</t>
   </si>
   <si>
@@ -438,6 +435,15 @@
   </si>
   <si>
     <t>Saturday 8/8/26</t>
+  </si>
+  <si>
+    <t>I will be hosting a $50 buy-in tournament on October 10th at 6:30 PM. Please RSVP via Partiful. If you'd like an invite, shoot me a message.</t>
+  </si>
+  <si>
+    <t>/photos/luck-casino.avif</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -771,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -985,6 +991,7 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1401,8 +1408,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EventPhotosTable" displayName="EventPhotosTable" ref="A4:E7" totalsRowShown="0">
-  <autoFilter ref="A4:E7" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EventPhotosTable" displayName="EventPhotosTable" ref="A4:E8" totalsRowShown="0">
+  <autoFilter ref="A4:E8" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Event ID" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Image Path"/>
@@ -1843,7 +1850,7 @@
       </c>
       <c r="H9" s="45">
         <f>COUNTA('Event Photos'!A5:A500)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1">
@@ -2352,7 +2359,7 @@
         <v>118</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D8" s="30">
         <v>46305</v>
@@ -3863,13 +3870,13 @@
     </row>
     <row r="9" spans="1:10" ht="24" customHeight="1">
       <c r="A9" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="D9" s="30">
         <v>46239</v>
@@ -3892,13 +3899,13 @@
     </row>
     <row r="10" spans="1:10" ht="24" customHeight="1">
       <c r="A10" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="D10" s="30">
         <v>46242</v>
@@ -4472,7 +4479,7 @@
     </row>
     <row r="39" spans="1:4" ht="24" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>69</v>
@@ -4486,7 +4493,7 @@
     </row>
     <row r="40" spans="1:4" ht="24" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>68</v>
@@ -4500,7 +4507,7 @@
     </row>
     <row r="41" spans="1:4" ht="24" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>51</v>
@@ -4514,10 +4521,10 @@
     </row>
     <row r="42" spans="1:4" ht="24" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C42" s="14">
         <v>20</v>
@@ -4528,7 +4535,7 @@
     </row>
     <row r="43" spans="1:4" ht="24" customHeight="1">
       <c r="A43" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>72</v>
@@ -4542,7 +4549,7 @@
     </row>
     <row r="44" spans="1:4" ht="24" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>67</v>
@@ -4556,7 +4563,7 @@
     </row>
     <row r="45" spans="1:4" ht="24" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>56</v>
@@ -4570,7 +4577,7 @@
     </row>
     <row r="46" spans="1:4" ht="24" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>71</v>
@@ -4584,7 +4591,7 @@
     </row>
     <row r="47" spans="1:4" ht="24" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>70</v>
@@ -4598,7 +4605,7 @@
     </row>
     <row r="48" spans="1:4" ht="24" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>104</v>
@@ -4612,7 +4619,7 @@
     </row>
     <row r="49" spans="1:4" ht="24" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>67</v>
@@ -4626,7 +4633,7 @@
     </row>
     <row r="50" spans="1:4" ht="24" customHeight="1">
       <c r="A50" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>72</v>
@@ -4640,7 +4647,7 @@
     </row>
     <row r="51" spans="1:4" ht="24" customHeight="1">
       <c r="A51" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>56</v>
@@ -4654,7 +4661,7 @@
     </row>
     <row r="52" spans="1:4" ht="24" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>71</v>
@@ -4668,7 +4675,7 @@
     </row>
     <row r="53" spans="1:4" ht="24" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>70</v>
@@ -4682,7 +4689,7 @@
     </row>
     <row r="54" spans="1:4" ht="24" customHeight="1">
       <c r="A54" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>69</v>
@@ -4696,7 +4703,7 @@
     </row>
     <row r="55" spans="1:4" ht="24" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>51</v>
@@ -4710,7 +4717,7 @@
     </row>
     <row r="56" spans="1:4" ht="24" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>68</v>
@@ -4747,7 +4754,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4876,6 +4883,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:5" ht="16">
+      <c r="A8" s="81" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
@@ -4883,10 +4901,10 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="D5:D7" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" sqref="D5:D8" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="E5:E7" xr:uid="{00000000-0002-0000-0500-000001000000}">
+    <dataValidation type="whole" sqref="E5:E8" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>1</formula1>
       <formula2>9999</formula2>
     </dataValidation>
@@ -5005,18 +5023,18 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="68">
+    <row r="5" spans="1:7" ht="51">
       <c r="A5" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B5" s="62">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="C5" s="60" t="s">
         <v>121</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>118</v>
@@ -5030,16 +5048,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" s="63">
         <v>46236</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="E6" s="61" t="s">
         <v>41</v>
@@ -5047,16 +5065,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B7" s="63">
         <v>46236</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="E7" s="61" t="s">
         <v>37</v>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9766D901-A242-BF45-BA9E-004931AAF88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6D2756-5182-F246-B5E1-B1DFF33124C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19540" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="142">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -446,13 +446,25 @@
     <t>8 PM</t>
   </si>
   <si>
-    <t>Saturday 8/15</t>
-  </si>
-  <si>
     <t>cash-game-2026-08-15</t>
   </si>
   <si>
     <t>Calvin A.</t>
+  </si>
+  <si>
+    <t>David B.</t>
+  </si>
+  <si>
+    <t>Dimple P.</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-19</t>
+  </si>
+  <si>
+    <t>Wednesday 8/19/26</t>
+  </si>
+  <si>
+    <t>Saturday 8/15/26</t>
   </si>
 </sst>
 </file>
@@ -954,6 +966,19 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -983,19 +1008,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1284,7 +1296,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I48" totalsRowShown="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="27">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="25"/>
@@ -1296,12 +1308,12 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="19"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="18"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I13" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1318,7 +1330,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D74" totalsRowShown="0" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D84" totalsRowShown="0" dataDxfId="17">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1567,106 +1579,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="66" t="s">
+      <c r="A1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="71" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="66" t="s">
+      <c r="A2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="71" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="72" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="73" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1674,22 +1686,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="70" t="s">
+      <c r="G6" s="75" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1701,22 +1713,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="71" t="s">
+      <c r="E7" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="77" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1728,49 +1740,49 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="70" t="s">
+      <c r="G8" s="75" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="71" t="s">
+      <c r="E9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="77" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1782,22 +1794,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="69" t="s">
+      <c r="D10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="69" t="s">
+      <c r="E10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="70" t="s">
+      <c r="G10" s="75" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -1809,209 +1821,209 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="77" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="73" t="s">
+      <c r="E14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="73" t="s">
+      <c r="F14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="73" t="s">
+      <c r="H14" s="78" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="69" t="s">
+      <c r="A15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="69" t="s">
+      <c r="D15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="69" t="s">
+      <c r="E15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="69" t="s">
+      <c r="F15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="69" t="s">
+      <c r="H15" s="74" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="71" t="s">
+      <c r="A16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="71" t="s">
+      <c r="D16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="71" t="s">
+      <c r="E16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="71" t="s">
+      <c r="G16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="71" t="s">
+      <c r="H16" s="76" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="69" t="s">
+      <c r="A17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="74" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="71" t="s">
+      <c r="E18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="71" t="s">
+      <c r="G18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="71" t="s">
+      <c r="H18" s="76" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="69" t="s">
+      <c r="A19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="69" t="s">
+      <c r="D19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="69" t="s">
+      <c r="E19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="69" t="s">
+      <c r="F19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="69" t="s">
+      <c r="G19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="69" t="s">
+      <c r="H19" s="74" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="71" t="s">
+      <c r="A20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="71" t="s">
+      <c r="E20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="71" t="s">
+      <c r="F20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="71" t="s">
+      <c r="G20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="71" t="s">
+      <c r="H20" s="76" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2064,89 +2076,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="F1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="74" t="s">
+      <c r="I1" s="79" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="75" t="s">
+      <c r="H2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="80" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="76" t="s">
+      <c r="I3" s="81" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2310,8 +2322,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:I57"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="27" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
@@ -2325,46 +2337,46 @@
     <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25" customHeight="1">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:9" ht="27" customHeight="1">
+      <c r="A1" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-    </row>
-    <row r="2" spans="1:9" ht="31" customHeight="1">
-      <c r="A2" s="79" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+    </row>
+    <row r="2" spans="1:9" ht="27" customHeight="1">
+      <c r="A2" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-    </row>
-    <row r="3" spans="1:9" ht="25" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+    </row>
+    <row r="3" spans="1:9" ht="27" customHeight="1">
+      <c r="A3" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-    </row>
-    <row r="4" spans="1:9" ht="34" customHeight="1">
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+    </row>
+    <row r="4" spans="1:9" ht="27" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -2393,7 +2405,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25" customHeight="1">
+    <row r="5" spans="1:9" ht="27" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>40</v>
       </c>
@@ -2416,7 +2428,7 @@
       <c r="H5" s="50"/>
       <c r="I5" s="51"/>
     </row>
-    <row r="6" spans="1:9" ht="25" customHeight="1">
+    <row r="6" spans="1:9" ht="27" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
@@ -2439,7 +2451,7 @@
       <c r="H6" s="52"/>
       <c r="I6" s="53"/>
     </row>
-    <row r="7" spans="1:9" ht="25" customHeight="1">
+    <row r="7" spans="1:9" ht="27" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>40</v>
       </c>
@@ -2462,7 +2474,7 @@
       <c r="H7" s="54"/>
       <c r="I7" s="55"/>
     </row>
-    <row r="8" spans="1:9" ht="25" customHeight="1">
+    <row r="8" spans="1:9" ht="27" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>40</v>
       </c>
@@ -2485,7 +2497,7 @@
       <c r="H8" s="52"/>
       <c r="I8" s="53"/>
     </row>
-    <row r="9" spans="1:9" ht="25" customHeight="1">
+    <row r="9" spans="1:9" ht="27" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>40</v>
       </c>
@@ -2508,7 +2520,7 @@
       <c r="H9" s="54"/>
       <c r="I9" s="55"/>
     </row>
-    <row r="10" spans="1:9" ht="25" customHeight="1">
+    <row r="10" spans="1:9" ht="27" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
@@ -2531,7 +2543,7 @@
       <c r="H10" s="52"/>
       <c r="I10" s="53"/>
     </row>
-    <row r="11" spans="1:9" ht="25" customHeight="1">
+    <row r="11" spans="1:9" ht="27" customHeight="1">
       <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
@@ -2554,7 +2566,7 @@
       <c r="H11" s="54"/>
       <c r="I11" s="55"/>
     </row>
-    <row r="12" spans="1:9" ht="25" customHeight="1">
+    <row r="12" spans="1:9" ht="27" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
@@ -2577,7 +2589,7 @@
       <c r="H12" s="52"/>
       <c r="I12" s="53"/>
     </row>
-    <row r="13" spans="1:9" ht="25" customHeight="1">
+    <row r="13" spans="1:9" ht="27" customHeight="1">
       <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
@@ -2600,7 +2612,7 @@
       <c r="H13" s="54"/>
       <c r="I13" s="55"/>
     </row>
-    <row r="14" spans="1:9" ht="25" customHeight="1">
+    <row r="14" spans="1:9" ht="27" customHeight="1">
       <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
@@ -2623,7 +2635,7 @@
       <c r="H14" s="52"/>
       <c r="I14" s="53"/>
     </row>
-    <row r="15" spans="1:9" ht="25" customHeight="1">
+    <row r="15" spans="1:9" ht="27" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>40</v>
       </c>
@@ -2646,7 +2658,7 @@
       <c r="H15" s="54"/>
       <c r="I15" s="55"/>
     </row>
-    <row r="16" spans="1:9" ht="25" customHeight="1">
+    <row r="16" spans="1:9" ht="27" customHeight="1">
       <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
@@ -2669,7 +2681,7 @@
       <c r="H16" s="54"/>
       <c r="I16" s="55"/>
     </row>
-    <row r="17" spans="1:9" ht="25" customHeight="1">
+    <row r="17" spans="1:9" ht="27" customHeight="1">
       <c r="A17" s="6" t="s">
         <v>40</v>
       </c>
@@ -2692,7 +2704,7 @@
       <c r="H17" s="52"/>
       <c r="I17" s="53"/>
     </row>
-    <row r="18" spans="1:9" ht="25" customHeight="1">
+    <row r="18" spans="1:9" ht="27" customHeight="1">
       <c r="A18" s="13" t="s">
         <v>40</v>
       </c>
@@ -2715,7 +2727,7 @@
       <c r="H18" s="54"/>
       <c r="I18" s="55"/>
     </row>
-    <row r="19" spans="1:9" ht="25" customHeight="1">
+    <row r="19" spans="1:9" ht="27" customHeight="1">
       <c r="A19" s="13" t="s">
         <v>40</v>
       </c>
@@ -2738,7 +2750,7 @@
       <c r="H19" s="52"/>
       <c r="I19" s="53"/>
     </row>
-    <row r="20" spans="1:9" ht="25" customHeight="1">
+    <row r="20" spans="1:9" ht="27" customHeight="1">
       <c r="A20" s="13" t="s">
         <v>40</v>
       </c>
@@ -2761,7 +2773,7 @@
       <c r="H20" s="54"/>
       <c r="I20" s="55"/>
     </row>
-    <row r="21" spans="1:9" ht="25" customHeight="1">
+    <row r="21" spans="1:9" ht="27" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>36</v>
       </c>
@@ -2784,7 +2796,7 @@
       <c r="H21" s="52"/>
       <c r="I21" s="53"/>
     </row>
-    <row r="22" spans="1:9" ht="25" customHeight="1">
+    <row r="22" spans="1:9" ht="27" customHeight="1">
       <c r="A22" s="13" t="s">
         <v>36</v>
       </c>
@@ -2807,7 +2819,7 @@
       <c r="H22" s="54"/>
       <c r="I22" s="55"/>
     </row>
-    <row r="23" spans="1:9" ht="25" customHeight="1">
+    <row r="23" spans="1:9" ht="27" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>36</v>
       </c>
@@ -2830,7 +2842,7 @@
       <c r="H23" s="52"/>
       <c r="I23" s="53"/>
     </row>
-    <row r="24" spans="1:9" ht="25" customHeight="1">
+    <row r="24" spans="1:9" ht="27" customHeight="1">
       <c r="A24" s="13" t="s">
         <v>36</v>
       </c>
@@ -2853,7 +2865,7 @@
       <c r="H24" s="54"/>
       <c r="I24" s="55"/>
     </row>
-    <row r="25" spans="1:9" ht="25" customHeight="1">
+    <row r="25" spans="1:9" ht="27" customHeight="1">
       <c r="A25" s="13" t="s">
         <v>36</v>
       </c>
@@ -2876,7 +2888,7 @@
       <c r="H25" s="52"/>
       <c r="I25" s="53"/>
     </row>
-    <row r="26" spans="1:9" ht="25" customHeight="1">
+    <row r="26" spans="1:9" ht="27" customHeight="1">
       <c r="A26" s="13" t="s">
         <v>36</v>
       </c>
@@ -2899,7 +2911,7 @@
       <c r="H26" s="54"/>
       <c r="I26" s="55"/>
     </row>
-    <row r="27" spans="1:9" ht="25" customHeight="1">
+    <row r="27" spans="1:9" ht="27" customHeight="1">
       <c r="A27" s="13" t="s">
         <v>36</v>
       </c>
@@ -2922,7 +2934,7 @@
       <c r="H27" s="52"/>
       <c r="I27" s="53"/>
     </row>
-    <row r="28" spans="1:9" ht="25" customHeight="1">
+    <row r="28" spans="1:9" ht="27" customHeight="1">
       <c r="A28" s="13" t="s">
         <v>36</v>
       </c>
@@ -2945,7 +2957,7 @@
       <c r="H28" s="54"/>
       <c r="I28" s="55"/>
     </row>
-    <row r="29" spans="1:9" ht="25" customHeight="1">
+    <row r="29" spans="1:9" ht="27" customHeight="1">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
@@ -2968,7 +2980,7 @@
       <c r="H29" s="52"/>
       <c r="I29" s="53"/>
     </row>
-    <row r="30" spans="1:9" ht="25" customHeight="1">
+    <row r="30" spans="1:9" ht="27" customHeight="1">
       <c r="A30" s="13" t="s">
         <v>36</v>
       </c>
@@ -2991,7 +3003,7 @@
       <c r="H30" s="54"/>
       <c r="I30" s="55"/>
     </row>
-    <row r="31" spans="1:9" ht="25" customHeight="1">
+    <row r="31" spans="1:9" ht="27" customHeight="1">
       <c r="A31" s="13" t="s">
         <v>36</v>
       </c>
@@ -3014,7 +3026,7 @@
       <c r="H31" s="52"/>
       <c r="I31" s="53"/>
     </row>
-    <row r="32" spans="1:9" ht="25" customHeight="1">
+    <row r="32" spans="1:9" ht="27" customHeight="1">
       <c r="A32" s="13" t="s">
         <v>36</v>
       </c>
@@ -3037,12 +3049,12 @@
       <c r="H32" s="54"/>
       <c r="I32" s="55"/>
     </row>
-    <row r="33" spans="1:9" ht="25" customHeight="1">
+    <row r="33" spans="1:9" ht="27" customHeight="1">
       <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="C33" s="14">
         <v>40</v>
@@ -3060,7 +3072,7 @@
       <c r="H33" s="52"/>
       <c r="I33" s="53"/>
     </row>
-    <row r="34" spans="1:9" ht="25" customHeight="1">
+    <row r="34" spans="1:9" ht="27" customHeight="1">
       <c r="A34" s="13" t="s">
         <v>36</v>
       </c>
@@ -3083,7 +3095,7 @@
       <c r="H34" s="54"/>
       <c r="I34" s="55"/>
     </row>
-    <row r="35" spans="1:9" ht="25" customHeight="1">
+    <row r="35" spans="1:9" ht="27" customHeight="1">
       <c r="A35" s="13" t="s">
         <v>42</v>
       </c>
@@ -3112,7 +3124,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="25" customHeight="1">
+    <row r="36" spans="1:9" ht="27" customHeight="1">
       <c r="A36" s="13" t="s">
         <v>42</v>
       </c>
@@ -3141,7 +3153,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="25" customHeight="1">
+    <row r="37" spans="1:9" ht="27" customHeight="1">
       <c r="A37" s="13" t="s">
         <v>42</v>
       </c>
@@ -3170,7 +3182,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="25" customHeight="1">
+    <row r="38" spans="1:9" ht="27" customHeight="1">
       <c r="A38" s="13" t="s">
         <v>42</v>
       </c>
@@ -3199,7 +3211,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="25" customHeight="1">
+    <row r="39" spans="1:9" ht="27" customHeight="1">
       <c r="A39" s="13" t="s">
         <v>42</v>
       </c>
@@ -3228,7 +3240,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="25" customHeight="1">
+    <row r="40" spans="1:9" ht="27" customHeight="1">
       <c r="A40" s="13" t="s">
         <v>42</v>
       </c>
@@ -3257,7 +3269,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="25" customHeight="1">
+    <row r="41" spans="1:9" ht="27" customHeight="1">
       <c r="A41" s="13" t="s">
         <v>42</v>
       </c>
@@ -3286,7 +3298,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="25" customHeight="1">
+    <row r="42" spans="1:9" ht="27" customHeight="1">
       <c r="A42" s="13" t="s">
         <v>42</v>
       </c>
@@ -3315,7 +3327,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="25" customHeight="1">
+    <row r="43" spans="1:9" ht="27" customHeight="1">
       <c r="A43" s="13" t="s">
         <v>42</v>
       </c>
@@ -3344,7 +3356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="25" customHeight="1">
+    <row r="44" spans="1:9" ht="27" customHeight="1">
       <c r="A44" s="13" t="s">
         <v>42</v>
       </c>
@@ -3373,7 +3385,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="25" customHeight="1">
+    <row r="45" spans="1:9" ht="27" customHeight="1">
       <c r="A45" s="13" t="s">
         <v>42</v>
       </c>
@@ -3402,7 +3414,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="25" customHeight="1">
+    <row r="46" spans="1:9" ht="27" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>42</v>
       </c>
@@ -3431,7 +3443,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="25" customHeight="1">
+    <row r="47" spans="1:9" ht="27" customHeight="1">
       <c r="A47" s="13" t="s">
         <v>42</v>
       </c>
@@ -3460,7 +3472,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="25" customHeight="1">
+    <row r="48" spans="1:9" ht="27" customHeight="1">
       <c r="A48" s="13" t="s">
         <v>42</v>
       </c>
@@ -3482,6 +3494,105 @@
       <c r="G48" s="49"/>
       <c r="H48" s="54"/>
       <c r="I48" s="55"/>
+    </row>
+    <row r="49" spans="1:3" ht="27" customHeight="1">
+      <c r="A49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="27" customHeight="1">
+      <c r="A50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="27" customHeight="1">
+      <c r="A51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="27" customHeight="1">
+      <c r="A52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="27" customHeight="1">
+      <c r="A53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="27" customHeight="1">
+      <c r="A54" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="27" customHeight="1">
+      <c r="A55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="27" customHeight="1">
+      <c r="A56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="27" customHeight="1">
+      <c r="A57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="14">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3508,7 +3619,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -3525,89 +3636,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="F1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="74" t="s">
+      <c r="I1" s="79" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="75" t="s">
+      <c r="H2" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="80" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="76" t="s">
+      <c r="I3" s="81" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3828,13 +3939,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D12" s="28">
         <v>46249</v>
@@ -3849,6 +3960,32 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="28">
+        <v>46253</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H13">
         <v>20</v>
       </c>
     </row>
@@ -3865,7 +4002,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="G5:G199 F5:F12" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="G5:G199 F5:F13" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -3882,7 +4019,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="27" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43" style="1" customWidth="1"/>
@@ -3893,20 +4030,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
     </row>
     <row r="2" spans="1:4" ht="27" customHeight="1">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
     </row>
     <row r="3" spans="1:4" ht="27" customHeight="1">
       <c r="A3" s="82" t="s">
@@ -4772,7 +4909,7 @@
     </row>
     <row r="65" spans="1:4" ht="27" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>46</v>
@@ -4786,7 +4923,7 @@
     </row>
     <row r="66" spans="1:4" ht="27" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>70</v>
@@ -4800,7 +4937,7 @@
     </row>
     <row r="67" spans="1:4" ht="27" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>71</v>
@@ -4814,7 +4951,7 @@
     </row>
     <row r="68" spans="1:4" ht="27" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>63</v>
@@ -4828,7 +4965,7 @@
     </row>
     <row r="69" spans="1:4" ht="27" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>68</v>
@@ -4842,10 +4979,10 @@
     </row>
     <row r="70" spans="1:4" ht="27" customHeight="1">
       <c r="A70" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C70" s="14">
         <v>20</v>
@@ -4856,7 +4993,7 @@
     </row>
     <row r="71" spans="1:4" ht="27" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>67</v>
@@ -4870,7 +5007,7 @@
     </row>
     <row r="72" spans="1:4" ht="27" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>62</v>
@@ -4884,7 +5021,7 @@
     </row>
     <row r="73" spans="1:4" ht="27" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>65</v>
@@ -4898,7 +5035,7 @@
     </row>
     <row r="74" spans="1:4" ht="27" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>64</v>
@@ -4908,6 +5045,146 @@
       </c>
       <c r="D74" s="14">
         <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="27" customHeight="1">
+      <c r="A75" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" s="14">
+        <v>30</v>
+      </c>
+      <c r="D75" s="14">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="27" customHeight="1">
+      <c r="A76" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C76" s="14">
+        <v>30</v>
+      </c>
+      <c r="D76" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="27" customHeight="1">
+      <c r="A77" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C77" s="14">
+        <v>20</v>
+      </c>
+      <c r="D77" s="14">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="27" customHeight="1">
+      <c r="A78" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C78" s="14">
+        <v>20</v>
+      </c>
+      <c r="D78" s="14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="27" customHeight="1">
+      <c r="A79" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C79" s="14">
+        <v>40</v>
+      </c>
+      <c r="D79" s="14">
+        <v>40.75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="27" customHeight="1">
+      <c r="A80" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C80" s="14">
+        <v>50</v>
+      </c>
+      <c r="D80" s="14">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="27" customHeight="1">
+      <c r="A81" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" s="14">
+        <v>20</v>
+      </c>
+      <c r="D81" s="14">
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="27" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C82" s="14">
+        <v>20</v>
+      </c>
+      <c r="D82" s="14">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="27" customHeight="1">
+      <c r="A83" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83" s="14">
+        <v>20</v>
+      </c>
+      <c r="D83" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="27" customHeight="1">
+      <c r="A84" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C84" s="14">
+        <v>100</v>
+      </c>
+      <c r="D84" s="14">
+        <v>25.25</v>
       </c>
     </row>
   </sheetData>
@@ -4946,53 +5223,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="79" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="80" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="81" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5113,71 +5390,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="F1" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="79" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="80" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="81" t="s">
         <v>122</v>
       </c>
     </row>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6D2756-5182-F246-B5E1-B1DFF33124C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CEC0139-07B3-2246-A6B3-5ACA771717FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19540" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="144">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -465,6 +465,12 @@
   </si>
   <si>
     <t>Saturday 8/15/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-22</t>
+  </si>
+  <si>
+    <t>Saturday 8/22/26</t>
   </si>
 </sst>
 </file>
@@ -969,49 +975,49 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1150,16 +1156,6 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1240,6 +1236,16 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1296,24 +1302,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="22">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I13" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I14" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1330,15 +1336,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D84" totalsRowShown="0" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D91" totalsRowShown="0" dataDxfId="27">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1579,106 +1585,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="71" t="s">
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="74" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="71" t="s">
+      <c r="A2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="74" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="72" t="s">
+      <c r="H3" s="75" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="73" t="s">
+      <c r="G5" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="73" t="s">
+      <c r="H5" s="76" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1686,22 +1692,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="74" t="s">
+      <c r="B6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="74" t="s">
+      <c r="D6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="74" t="s">
+      <c r="E6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="75" t="s">
+      <c r="G6" s="71" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1713,22 +1719,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="76" t="s">
+      <c r="D7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="77" t="s">
+      <c r="G7" s="72" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1740,49 +1746,49 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="74" t="s">
+      <c r="E8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="75" t="s">
+      <c r="G8" s="71" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="76" t="s">
+      <c r="C9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="72" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1794,22 +1800,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="74" t="s">
+      <c r="C10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="74" t="s">
+      <c r="E10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="75" t="s">
+      <c r="F10" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="75" t="s">
+      <c r="G10" s="71" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -1821,237 +1827,237 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="76" t="s">
+      <c r="D11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="77" t="s">
+      <c r="G11" s="72" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="78" t="s">
+      <c r="D14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="78" t="s">
+      <c r="F14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="78" t="s">
+      <c r="G14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="73" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="74" t="s">
+      <c r="A15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="74" t="s">
+      <c r="D15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="74" t="s">
+      <c r="E15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="74" t="s">
+      <c r="F15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="74" t="s">
+      <c r="G15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="74" t="s">
+      <c r="H15" s="70" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="76" t="s">
+      <c r="B16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="76" t="s">
+      <c r="E16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="76" t="s">
+      <c r="F16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="76" t="s">
+      <c r="G16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="76" t="s">
+      <c r="H16" s="69" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="74" t="s">
+      <c r="A17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="70" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="76" t="s">
+      <c r="A18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="76" t="s">
+      <c r="F18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="76" t="s">
+      <c r="G18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="76" t="s">
+      <c r="H18" s="69" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="74" t="s">
+      <c r="A19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="74" t="s">
+      <c r="C19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="D19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="74" t="s">
+      <c r="E19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="74" t="s">
+      <c r="F19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="74" t="s">
+      <c r="G19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="74" t="s">
+      <c r="H19" s="70" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="76" t="s">
+      <c r="E20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="76" t="s">
+      <c r="G20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="76" t="s">
+      <c r="H20" s="69" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2076,89 +2082,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="79" t="s">
+      <c r="H1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="77" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="78" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="81" t="s">
+      <c r="F3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="81" t="s">
+      <c r="G3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="81" t="s">
+      <c r="I3" s="79" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2347,34 +2353,34 @@
       <c r="E1" s="66"/>
       <c r="F1" s="66"/>
       <c r="G1" s="66"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
     </row>
     <row r="2" spans="1:9" ht="27" customHeight="1">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
     </row>
     <row r="3" spans="1:9" ht="27" customHeight="1">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -3619,7 +3625,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -3636,89 +3642,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="79" t="s">
+      <c r="H1" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="77" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="78" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="81" t="s">
+      <c r="F3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="81" t="s">
+      <c r="G3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="81" t="s">
+      <c r="I3" s="79" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3986,6 +3992,32 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="28">
+        <v>46256</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H14">
         <v>20</v>
       </c>
     </row>
@@ -4002,7 +4034,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="G5:G199 F5:F13" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="G5:G199 F5:F14" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4019,17 +4051,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D84"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="27" customHeight="1"/>
+  <dimension ref="A1:D91"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="23" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="21.1640625" style="14" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" style="14" customWidth="1"/>
     <col min="5" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27" customHeight="1">
+    <row r="1" spans="1:4" ht="23" customHeight="1">
       <c r="A1" s="66" t="s">
         <v>96</v>
       </c>
@@ -4037,23 +4069,23 @@
       <c r="C1" s="66"/>
       <c r="D1" s="66"/>
     </row>
-    <row r="2" spans="1:4" ht="27" customHeight="1">
-      <c r="A2" s="68" t="s">
+    <row r="2" spans="1:4" ht="23" customHeight="1">
+      <c r="A2" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-    </row>
-    <row r="3" spans="1:4" ht="27" customHeight="1">
-      <c r="A3" s="82" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+    </row>
+    <row r="3" spans="1:4" ht="23" customHeight="1">
+      <c r="A3" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-    </row>
-    <row r="4" spans="1:4" ht="27" customHeight="1">
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+    </row>
+    <row r="4" spans="1:4" ht="23" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>81</v>
       </c>
@@ -4067,7 +4099,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27" customHeight="1">
+    <row r="5" spans="1:4" ht="23" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>82</v>
       </c>
@@ -4081,7 +4113,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27" customHeight="1">
+    <row r="6" spans="1:4" ht="23" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>82</v>
       </c>
@@ -4095,7 +4127,7 @@
         <v>41.25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1">
+    <row r="7" spans="1:4" ht="23" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>82</v>
       </c>
@@ -4109,7 +4141,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27" customHeight="1">
+    <row r="8" spans="1:4" ht="23" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>82</v>
       </c>
@@ -4123,7 +4155,7 @@
         <v>48.55</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27" customHeight="1">
+    <row r="9" spans="1:4" ht="23" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>82</v>
       </c>
@@ -4137,7 +4169,7 @@
         <v>23.25</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="27" customHeight="1">
+    <row r="10" spans="1:4" ht="23" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>82</v>
       </c>
@@ -4151,7 +4183,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="27" customHeight="1">
+    <row r="11" spans="1:4" ht="23" customHeight="1">
       <c r="A11" s="13" t="s">
         <v>82</v>
       </c>
@@ -4165,7 +4197,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="27" customHeight="1">
+    <row r="12" spans="1:4" ht="23" customHeight="1">
       <c r="A12" s="13" t="s">
         <v>82</v>
       </c>
@@ -4179,7 +4211,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="27" customHeight="1">
+    <row r="13" spans="1:4" ht="23" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>82</v>
       </c>
@@ -4193,7 +4225,7 @@
         <v>30.05</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="27" customHeight="1">
+    <row r="14" spans="1:4" ht="23" customHeight="1">
       <c r="A14" s="13" t="s">
         <v>84</v>
       </c>
@@ -4207,7 +4239,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="27" customHeight="1">
+    <row r="15" spans="1:4" ht="23" customHeight="1">
       <c r="A15" s="13" t="s">
         <v>84</v>
       </c>
@@ -4221,7 +4253,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="27" customHeight="1">
+    <row r="16" spans="1:4" ht="23" customHeight="1">
       <c r="A16" s="13" t="s">
         <v>84</v>
       </c>
@@ -4235,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="27" customHeight="1">
+    <row r="17" spans="1:4" ht="23" customHeight="1">
       <c r="A17" s="13" t="s">
         <v>84</v>
       </c>
@@ -4249,7 +4281,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="27" customHeight="1">
+    <row r="18" spans="1:4" ht="23" customHeight="1">
       <c r="A18" s="13" t="s">
         <v>84</v>
       </c>
@@ -4263,7 +4295,7 @@
         <v>143.9</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="27" customHeight="1">
+    <row r="19" spans="1:4" ht="23" customHeight="1">
       <c r="A19" s="13" t="s">
         <v>84</v>
       </c>
@@ -4277,7 +4309,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="27" customHeight="1">
+    <row r="20" spans="1:4" ht="23" customHeight="1">
       <c r="A20" s="13" t="s">
         <v>84</v>
       </c>
@@ -4291,7 +4323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="27" customHeight="1">
+    <row r="21" spans="1:4" ht="23" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>84</v>
       </c>
@@ -4305,7 +4337,7 @@
         <v>148.9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="27" customHeight="1">
+    <row r="22" spans="1:4" ht="23" customHeight="1">
       <c r="A22" s="13" t="s">
         <v>86</v>
       </c>
@@ -4319,7 +4351,7 @@
         <v>73.75</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="27" customHeight="1">
+    <row r="23" spans="1:4" ht="23" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>86</v>
       </c>
@@ -4333,7 +4365,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="27" customHeight="1">
+    <row r="24" spans="1:4" ht="23" customHeight="1">
       <c r="A24" s="13" t="s">
         <v>86</v>
       </c>
@@ -4347,7 +4379,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="27" customHeight="1">
+    <row r="25" spans="1:4" ht="23" customHeight="1">
       <c r="A25" s="13" t="s">
         <v>86</v>
       </c>
@@ -4361,7 +4393,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="27" customHeight="1">
+    <row r="26" spans="1:4" ht="23" customHeight="1">
       <c r="A26" s="13" t="s">
         <v>86</v>
       </c>
@@ -4375,7 +4407,7 @@
         <v>23.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="27" customHeight="1">
+    <row r="27" spans="1:4" ht="23" customHeight="1">
       <c r="A27" s="13" t="s">
         <v>86</v>
       </c>
@@ -4389,7 +4421,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="27" customHeight="1">
+    <row r="28" spans="1:4" ht="23" customHeight="1">
       <c r="A28" s="13" t="s">
         <v>86</v>
       </c>
@@ -4403,7 +4435,7 @@
         <v>30.25</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="27" customHeight="1">
+    <row r="29" spans="1:4" ht="23" customHeight="1">
       <c r="A29" s="13" t="s">
         <v>86</v>
       </c>
@@ -4417,7 +4449,7 @@
         <v>34.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="27" customHeight="1">
+    <row r="30" spans="1:4" ht="23" customHeight="1">
       <c r="A30" s="13" t="s">
         <v>86</v>
       </c>
@@ -4431,7 +4463,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="27" customHeight="1">
+    <row r="31" spans="1:4" ht="23" customHeight="1">
       <c r="A31" s="13" t="s">
         <v>88</v>
       </c>
@@ -4445,7 +4477,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="27" customHeight="1">
+    <row r="32" spans="1:4" ht="23" customHeight="1">
       <c r="A32" s="13" t="s">
         <v>88</v>
       </c>
@@ -4459,7 +4491,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="27" customHeight="1">
+    <row r="33" spans="1:4" ht="23" customHeight="1">
       <c r="A33" s="13" t="s">
         <v>88</v>
       </c>
@@ -4473,7 +4505,7 @@
         <v>47.75</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="27" customHeight="1">
+    <row r="34" spans="1:4" ht="23" customHeight="1">
       <c r="A34" s="13" t="s">
         <v>88</v>
       </c>
@@ -4487,7 +4519,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="27" customHeight="1">
+    <row r="35" spans="1:4" ht="23" customHeight="1">
       <c r="A35" s="13" t="s">
         <v>88</v>
       </c>
@@ -4501,7 +4533,7 @@
         <v>24.25</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="27" customHeight="1">
+    <row r="36" spans="1:4" ht="23" customHeight="1">
       <c r="A36" s="13" t="s">
         <v>88</v>
       </c>
@@ -4515,7 +4547,7 @@
         <v>48.25</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="27" customHeight="1">
+    <row r="37" spans="1:4" ht="23" customHeight="1">
       <c r="A37" s="13" t="s">
         <v>88</v>
       </c>
@@ -4529,7 +4561,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="27" customHeight="1">
+    <row r="38" spans="1:4" ht="23" customHeight="1">
       <c r="A38" s="13" t="s">
         <v>88</v>
       </c>
@@ -4543,7 +4575,7 @@
         <v>73.25</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="27" customHeight="1">
+    <row r="39" spans="1:4" ht="23" customHeight="1">
       <c r="A39" s="13" t="s">
         <v>90</v>
       </c>
@@ -4557,7 +4589,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="27" customHeight="1">
+    <row r="40" spans="1:4" ht="23" customHeight="1">
       <c r="A40" s="13" t="s">
         <v>90</v>
       </c>
@@ -4571,7 +4603,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="27" customHeight="1">
+    <row r="41" spans="1:4" ht="23" customHeight="1">
       <c r="A41" s="13" t="s">
         <v>90</v>
       </c>
@@ -4585,7 +4617,7 @@
         <v>29.25</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="27" customHeight="1">
+    <row r="42" spans="1:4" ht="23" customHeight="1">
       <c r="A42" s="13" t="s">
         <v>90</v>
       </c>
@@ -4599,7 +4631,7 @@
         <v>23.75</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="27" customHeight="1">
+    <row r="43" spans="1:4" ht="23" customHeight="1">
       <c r="A43" s="13" t="s">
         <v>90</v>
       </c>
@@ -4613,7 +4645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="27" customHeight="1">
+    <row r="44" spans="1:4" ht="23" customHeight="1">
       <c r="A44" s="13" t="s">
         <v>90</v>
       </c>
@@ -4627,7 +4659,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="27" customHeight="1">
+    <row r="45" spans="1:4" ht="23" customHeight="1">
       <c r="A45" s="13" t="s">
         <v>90</v>
       </c>
@@ -4641,7 +4673,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="27" customHeight="1">
+    <row r="46" spans="1:4" ht="23" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>90</v>
       </c>
@@ -4655,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="27" customHeight="1">
+    <row r="47" spans="1:4" ht="23" customHeight="1">
       <c r="A47" s="13" t="s">
         <v>90</v>
       </c>
@@ -4669,7 +4701,7 @@
         <v>73.75</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="27" customHeight="1">
+    <row r="48" spans="1:4" ht="23" customHeight="1">
       <c r="A48" s="13" t="s">
         <v>90</v>
       </c>
@@ -4683,7 +4715,7 @@
         <v>36.75</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="27" customHeight="1">
+    <row r="49" spans="1:4" ht="23" customHeight="1">
       <c r="A49" s="13" t="s">
         <v>92</v>
       </c>
@@ -4697,7 +4729,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="27" customHeight="1">
+    <row r="50" spans="1:4" ht="23" customHeight="1">
       <c r="A50" s="13" t="s">
         <v>92</v>
       </c>
@@ -4711,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="27" customHeight="1">
+    <row r="51" spans="1:4" ht="23" customHeight="1">
       <c r="A51" s="13" t="s">
         <v>92</v>
       </c>
@@ -4725,7 +4757,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="27" customHeight="1">
+    <row r="52" spans="1:4" ht="23" customHeight="1">
       <c r="A52" s="13" t="s">
         <v>92</v>
       </c>
@@ -4739,7 +4771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="27" customHeight="1">
+    <row r="53" spans="1:4" ht="23" customHeight="1">
       <c r="A53" s="13" t="s">
         <v>92</v>
       </c>
@@ -4753,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="27" customHeight="1">
+    <row r="54" spans="1:4" ht="23" customHeight="1">
       <c r="A54" s="13" t="s">
         <v>92</v>
       </c>
@@ -4767,7 +4799,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="27" customHeight="1">
+    <row r="55" spans="1:4" ht="23" customHeight="1">
       <c r="A55" s="13" t="s">
         <v>92</v>
       </c>
@@ -4781,7 +4813,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="27" customHeight="1">
+    <row r="56" spans="1:4" ht="23" customHeight="1">
       <c r="A56" s="13" t="s">
         <v>92</v>
       </c>
@@ -4795,7 +4827,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="27" customHeight="1">
+    <row r="57" spans="1:4" ht="23" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>94</v>
       </c>
@@ -4809,7 +4841,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="27" customHeight="1">
+    <row r="58" spans="1:4" ht="23" customHeight="1">
       <c r="A58" s="1" t="s">
         <v>94</v>
       </c>
@@ -4823,7 +4855,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="27" customHeight="1">
+    <row r="59" spans="1:4" ht="23" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>94</v>
       </c>
@@ -4837,7 +4869,7 @@
         <v>37.700000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="27" customHeight="1">
+    <row r="60" spans="1:4" ht="23" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>94</v>
       </c>
@@ -4851,7 +4883,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="27" customHeight="1">
+    <row r="61" spans="1:4" ht="23" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>94</v>
       </c>
@@ -4865,7 +4897,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="27" customHeight="1">
+    <row r="62" spans="1:4" ht="23" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>94</v>
       </c>
@@ -4879,7 +4911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="27" customHeight="1">
+    <row r="63" spans="1:4" ht="23" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>94</v>
       </c>
@@ -4893,7 +4925,7 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="27" customHeight="1">
+    <row r="64" spans="1:4" ht="23" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>94</v>
       </c>
@@ -4907,7 +4939,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="27" customHeight="1">
+    <row r="65" spans="1:4" ht="23" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>135</v>
       </c>
@@ -4921,7 +4953,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="27" customHeight="1">
+    <row r="66" spans="1:4" ht="23" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>135</v>
       </c>
@@ -4935,7 +4967,7 @@
         <v>43.75</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="27" customHeight="1">
+    <row r="67" spans="1:4" ht="23" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>135</v>
       </c>
@@ -4949,7 +4981,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="27" customHeight="1">
+    <row r="68" spans="1:4" ht="23" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>135</v>
       </c>
@@ -4963,7 +4995,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="27" customHeight="1">
+    <row r="69" spans="1:4" ht="23" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>135</v>
       </c>
@@ -4977,7 +5009,7 @@
         <v>75.25</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="27" customHeight="1">
+    <row r="70" spans="1:4" ht="23" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>135</v>
       </c>
@@ -4991,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="27" customHeight="1">
+    <row r="71" spans="1:4" ht="23" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>135</v>
       </c>
@@ -5005,7 +5037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="27" customHeight="1">
+    <row r="72" spans="1:4" ht="23" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>135</v>
       </c>
@@ -5019,7 +5051,7 @@
         <v>24.25</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="27" customHeight="1">
+    <row r="73" spans="1:4" ht="23" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>135</v>
       </c>
@@ -5033,7 +5065,7 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="27" customHeight="1">
+    <row r="74" spans="1:4" ht="23" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>135</v>
       </c>
@@ -5047,7 +5079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="27" customHeight="1">
+    <row r="75" spans="1:4" ht="23" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>139</v>
       </c>
@@ -5061,7 +5093,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="27" customHeight="1">
+    <row r="76" spans="1:4" ht="23" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>139</v>
       </c>
@@ -5075,7 +5107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="27" customHeight="1">
+    <row r="77" spans="1:4" ht="23" customHeight="1">
       <c r="A77" s="1" t="s">
         <v>139</v>
       </c>
@@ -5089,7 +5121,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="27" customHeight="1">
+    <row r="78" spans="1:4" ht="23" customHeight="1">
       <c r="A78" s="1" t="s">
         <v>139</v>
       </c>
@@ -5103,7 +5135,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="27" customHeight="1">
+    <row r="79" spans="1:4" ht="23" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>139</v>
       </c>
@@ -5117,7 +5149,7 @@
         <v>40.75</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="27" customHeight="1">
+    <row r="80" spans="1:4" ht="23" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>139</v>
       </c>
@@ -5131,7 +5163,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="27" customHeight="1">
+    <row r="81" spans="1:4" ht="23" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>139</v>
       </c>
@@ -5145,7 +5177,7 @@
         <v>81.25</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="27" customHeight="1">
+    <row r="82" spans="1:4" ht="23" customHeight="1">
       <c r="A82" s="1" t="s">
         <v>139</v>
       </c>
@@ -5159,7 +5191,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="27" customHeight="1">
+    <row r="83" spans="1:4" ht="23" customHeight="1">
       <c r="A83" s="1" t="s">
         <v>139</v>
       </c>
@@ -5173,7 +5205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="27" customHeight="1">
+    <row r="84" spans="1:4" ht="23" customHeight="1">
       <c r="A84" s="1" t="s">
         <v>139</v>
       </c>
@@ -5185,6 +5217,104 @@
       </c>
       <c r="D84" s="14">
         <v>25.25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="23" customHeight="1">
+      <c r="A85" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C85" s="14">
+        <v>40</v>
+      </c>
+      <c r="D85" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="23" customHeight="1">
+      <c r="A86" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" s="14">
+        <v>40</v>
+      </c>
+      <c r="D86" s="14">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="23" customHeight="1">
+      <c r="A87" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C87" s="14">
+        <v>20</v>
+      </c>
+      <c r="D87" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="23" customHeight="1">
+      <c r="A88" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C88" s="14">
+        <v>20</v>
+      </c>
+      <c r="D88" s="14">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="23" customHeight="1">
+      <c r="A89" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C89" s="14">
+        <v>40</v>
+      </c>
+      <c r="D89" s="14">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="23" customHeight="1">
+      <c r="A90" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C90" s="14">
+        <v>40</v>
+      </c>
+      <c r="D90" s="14">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="23" customHeight="1">
+      <c r="A91" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C91" s="14">
+        <v>40</v>
+      </c>
+      <c r="D91" s="14">
+        <v>12.2</v>
       </c>
     </row>
   </sheetData>
@@ -5223,53 +5353,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="77" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="78" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="79" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5390,71 +5520,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="77" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="78" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="F3" s="81" t="s">
+      <c r="F3" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="81" t="s">
+      <c r="G3" s="79" t="s">
         <v>122</v>
       </c>
     </row>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CEC0139-07B3-2246-A6B3-5ACA771717FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6467D06-C787-5649-8CC4-615E583F297C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -981,28 +981,28 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1585,106 +1585,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="74" t="s">
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="69" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="74" t="s">
+      <c r="A2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="69" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="75" t="s">
+      <c r="H3" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="76" t="s">
+      <c r="D5" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="F5" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="76" t="s">
+      <c r="G5" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="71" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1692,22 +1692,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="E6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="71" t="s">
+      <c r="G6" s="73" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1719,22 +1719,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="75" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1746,22 +1746,22 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="71" t="s">
+      <c r="G8" s="73" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
@@ -1773,22 +1773,22 @@
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="69" t="s">
+      <c r="E9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="75" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1800,22 +1800,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="71" t="s">
+      <c r="G10" s="73" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -1827,22 +1827,22 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="75" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
@@ -1852,212 +1852,212 @@
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="73" t="s">
+      <c r="E14" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="73" t="s">
+      <c r="F14" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="73" t="s">
+      <c r="H14" s="76" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="70" t="s">
+      <c r="E15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="70" t="s">
+      <c r="F15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="70" t="s">
+      <c r="G15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="70" t="s">
+      <c r="H15" s="72" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="69" t="s">
+      <c r="A16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="69" t="s">
+      <c r="E16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="69" t="s">
+      <c r="F16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="69" t="s">
+      <c r="H16" s="74" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="70" t="s">
+      <c r="A17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="72" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="69" t="s">
+      <c r="A18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="69" t="s">
+      <c r="D18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="69" t="s">
+      <c r="E18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="69" t="s">
+      <c r="F18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="69" t="s">
+      <c r="G18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="69" t="s">
+      <c r="H18" s="74" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="70" t="s">
+      <c r="D19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="70" t="s">
+      <c r="E19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="70" t="s">
+      <c r="F19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="70" t="s">
+      <c r="G19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="70" t="s">
+      <c r="H19" s="72" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="69" t="s">
+      <c r="F20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="69" t="s">
+      <c r="G20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="69" t="s">
+      <c r="H20" s="74" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5280,7 +5280,7 @@
         <v>142</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C89" s="14">
         <v>40</v>
@@ -5294,7 +5294,7 @@
         <v>142</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C90" s="14">
         <v>40</v>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6467D06-C787-5649-8CC4-615E583F297C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91DA6F1-27F5-C84E-A616-7EA6C4100AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="146">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -471,6 +471,12 @@
   </si>
   <si>
     <t>Saturday 8/22/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-26</t>
+  </si>
+  <si>
+    <t>Wednesday 8/26/26</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1325,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I15" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1336,7 +1342,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D91" totalsRowShown="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D98" totalsRowShown="0" dataDxfId="27">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1766,7 +1772,7 @@
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
@@ -1847,7 +1853,7 @@
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
@@ -3625,7 +3631,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -4021,6 +4027,32 @@
         <v>20</v>
       </c>
     </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="28">
+        <v>46260</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H15">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
@@ -4034,7 +4066,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="G5:G199 F5:F14" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="G5:G199 F5:F15" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4051,7 +4083,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -5315,6 +5347,104 @@
       </c>
       <c r="D91" s="14">
         <v>12.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="23" customHeight="1">
+      <c r="A92" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C92" s="14">
+        <v>40</v>
+      </c>
+      <c r="D92" s="14">
+        <v>34.75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="23" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C93" s="14">
+        <v>20</v>
+      </c>
+      <c r="D93" s="14">
+        <v>25.75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="23" customHeight="1">
+      <c r="A94" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C94" s="14">
+        <v>20</v>
+      </c>
+      <c r="D94" s="14">
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="23" customHeight="1">
+      <c r="A95" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C95" s="14">
+        <v>20</v>
+      </c>
+      <c r="D95" s="14">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="23" customHeight="1">
+      <c r="A96" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C96" s="14">
+        <v>40</v>
+      </c>
+      <c r="D96" s="14">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="23" customHeight="1">
+      <c r="A97" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C97" s="14">
+        <v>20</v>
+      </c>
+      <c r="D97" s="14">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="23" customHeight="1">
+      <c r="A98" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C98" s="14">
+        <v>40</v>
+      </c>
+      <c r="D98" s="14">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91DA6F1-27F5-C84E-A616-7EA6C4100AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AF17B6-5C39-C741-AFC5-7302A6E68036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="148">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -477,6 +477,12 @@
   </si>
   <si>
     <t>Wednesday 8/26/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-29</t>
+  </si>
+  <si>
+    <t>Saturday 8/29/26</t>
   </si>
 </sst>
 </file>
@@ -987,6 +993,19 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -996,19 +1015,6 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1325,7 +1331,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I15" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I16" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1342,7 +1348,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D98" totalsRowShown="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D105" totalsRowShown="0" dataDxfId="27">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1591,106 +1597,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="69" t="s">
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="74" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="69" t="s">
+      <c r="A2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="74" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="70" t="s">
+      <c r="E3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="70" t="s">
+      <c r="H3" s="75" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="71" t="s">
+      <c r="E5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F5" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="71" t="s">
+      <c r="H5" s="76" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1698,22 +1704,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="72" t="s">
+      <c r="E6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="73" t="s">
+      <c r="G6" s="71" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1725,22 +1731,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="74" t="s">
+      <c r="E7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="75" t="s">
+      <c r="G7" s="72" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1752,49 +1758,49 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="73" t="s">
+      <c r="G8" s="71" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="74" t="s">
+      <c r="D9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="74" t="s">
+      <c r="E9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="75" t="s">
+      <c r="F9" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="75" t="s">
+      <c r="G9" s="72" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1806,22 +1812,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="73" t="s">
+      <c r="F10" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="71" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -1833,237 +1839,237 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="74" t="s">
+      <c r="E11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="75" t="s">
+      <c r="G11" s="72" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="76" t="s">
+      <c r="E14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="76" t="s">
+      <c r="G14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="76" t="s">
+      <c r="H14" s="73" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="72" t="s">
+      <c r="E15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="72" t="s">
+      <c r="F15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="72" t="s">
+      <c r="G15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="72" t="s">
+      <c r="H15" s="70" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="74" t="s">
+      <c r="A16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="74" t="s">
+      <c r="D16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="74" t="s">
+      <c r="E16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="74" t="s">
+      <c r="F16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="74" t="s">
+      <c r="G16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="74" t="s">
+      <c r="H16" s="69" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="72" t="s">
+      <c r="A17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="70" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="74" t="s">
+      <c r="A18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="74" t="s">
+      <c r="C18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="74" t="s">
+      <c r="D18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="74" t="s">
+      <c r="E18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="74" t="s">
+      <c r="F18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="74" t="s">
+      <c r="G18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="74" t="s">
+      <c r="H18" s="69" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="E19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="72" t="s">
+      <c r="G19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="72" t="s">
+      <c r="H19" s="70" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="74" t="s">
+      <c r="C20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="74" t="s">
+      <c r="D20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="74" t="s">
+      <c r="E20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="74" t="s">
+      <c r="F20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="74" t="s">
+      <c r="G20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="74" t="s">
+      <c r="H20" s="69" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3631,8 +3637,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
     <col min="2" max="2" width="27" style="1" customWidth="1"/>
@@ -3647,7 +3653,7 @@
     <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" customHeight="1">
+    <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="77" t="s">
         <v>79</v>
       </c>
@@ -3676,7 +3682,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="24" customHeight="1">
+    <row r="2" spans="1:9" ht="20" customHeight="1">
       <c r="A2" s="78" t="s">
         <v>80</v>
       </c>
@@ -3705,7 +3711,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" customHeight="1">
+    <row r="3" spans="1:9" ht="20" customHeight="1">
       <c r="A3" s="79" t="s">
         <v>26</v>
       </c>
@@ -3734,7 +3740,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="24" customHeight="1">
+    <row r="4" spans="1:9" ht="20" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>81</v>
       </c>
@@ -3763,7 +3769,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="24" customHeight="1">
+    <row r="5" spans="1:9" ht="20" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>82</v>
       </c>
@@ -3790,7 +3796,7 @@
       </c>
       <c r="I5" s="32"/>
     </row>
-    <row r="6" spans="1:9" ht="24" customHeight="1">
+    <row r="6" spans="1:9" ht="20" customHeight="1">
       <c r="A6" s="13" t="s">
         <v>84</v>
       </c>
@@ -3817,7 +3823,7 @@
       </c>
       <c r="I6" s="33"/>
     </row>
-    <row r="7" spans="1:9" ht="24" customHeight="1">
+    <row r="7" spans="1:9" ht="20" customHeight="1">
       <c r="A7" s="13" t="s">
         <v>86</v>
       </c>
@@ -3844,7 +3850,7 @@
       </c>
       <c r="I7" s="33"/>
     </row>
-    <row r="8" spans="1:9" ht="24" customHeight="1">
+    <row r="8" spans="1:9" ht="20" customHeight="1">
       <c r="A8" s="13" t="s">
         <v>88</v>
       </c>
@@ -3871,7 +3877,7 @@
       </c>
       <c r="I8" s="33"/>
     </row>
-    <row r="9" spans="1:9" ht="24" customHeight="1">
+    <row r="9" spans="1:9" ht="20" customHeight="1">
       <c r="A9" s="13" t="s">
         <v>90</v>
       </c>
@@ -3897,7 +3903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="24" customHeight="1">
+    <row r="10" spans="1:9" ht="20" customHeight="1">
       <c r="A10" s="13" t="s">
         <v>92</v>
       </c>
@@ -3923,7 +3929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="24" customHeight="1">
+    <row r="11" spans="1:9" ht="20" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>94</v>
       </c>
@@ -3949,7 +3955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" ht="20" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>135</v>
       </c>
@@ -3975,7 +3981,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" ht="20" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>139</v>
       </c>
@@ -4001,7 +4007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" ht="20" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>142</v>
       </c>
@@ -4027,7 +4033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" ht="20" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>144</v>
       </c>
@@ -4050,6 +4056,32 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="20" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H16">
         <v>20</v>
       </c>
     </row>
@@ -4066,7 +4098,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="G5:G199 F5:F15" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="G5:G199 F5:F16" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4083,7 +4115,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -5445,6 +5477,104 @@
       </c>
       <c r="D98" s="14">
         <v>32</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="23" customHeight="1">
+      <c r="A99" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C99" s="14">
+        <v>60</v>
+      </c>
+      <c r="D99" s="14">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="23" customHeight="1">
+      <c r="A100" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C100" s="14">
+        <v>80</v>
+      </c>
+      <c r="D100" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="23" customHeight="1">
+      <c r="A101" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C101" s="14">
+        <v>25</v>
+      </c>
+      <c r="D101" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="23" customHeight="1">
+      <c r="A102" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C102" s="14">
+        <v>40</v>
+      </c>
+      <c r="D102" s="14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="23" customHeight="1">
+      <c r="A103" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C103" s="14">
+        <v>40</v>
+      </c>
+      <c r="D103" s="14">
+        <v>104.1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="23" customHeight="1">
+      <c r="A104" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" s="14">
+        <v>60</v>
+      </c>
+      <c r="D104" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="23" customHeight="1">
+      <c r="A105" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C105" s="14">
+        <v>20</v>
+      </c>
+      <c r="D105" s="14">
+        <v>157.19999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AF17B6-5C39-C741-AFC5-7302A6E68036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045395FB-741A-744E-9E6A-EC157686C7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Cash Game Results" sheetId="5" r:id="rId5"/>
     <sheet name="Event Photos" sheetId="6" r:id="rId6"/>
     <sheet name="Announcements" sheetId="7" r:id="rId7"/>
+    <sheet name="Blind Schedules" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="156">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -275,9 +276,15 @@
     <t>2</t>
   </si>
   <si>
+    <t>David B.</t>
+  </si>
+  <si>
     <t>Ethan N.</t>
   </si>
   <si>
+    <t>Dimple P.</t>
+  </si>
+  <si>
     <t>CASH GAMES</t>
   </si>
   <si>
@@ -293,6 +300,9 @@
     <t>Wednesday 7/15/26</t>
   </si>
   <si>
+    <t>8 PM</t>
+  </si>
+  <si>
     <t>cash-game-2026-07-18</t>
   </si>
   <si>
@@ -329,6 +339,36 @@
     <t>Wednesday 8/12/26</t>
   </si>
   <si>
+    <t>cash-game-2026-08-15</t>
+  </si>
+  <si>
+    <t>Saturday 8/15/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-19</t>
+  </si>
+  <si>
+    <t>Wednesday 8/19/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-22</t>
+  </si>
+  <si>
+    <t>Saturday 8/22/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-26</t>
+  </si>
+  <si>
+    <t>Wednesday 8/26/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-08-29</t>
+  </si>
+  <si>
+    <t>Saturday 8/29/26</t>
+  </si>
+  <si>
     <t>CASH GAME RESULTS</t>
   </si>
   <si>
@@ -350,6 +390,9 @@
     <t>Ally K.</t>
   </si>
   <si>
+    <t>Calvin A.</t>
+  </si>
+  <si>
     <t>EVENT PHOTOS</t>
   </si>
   <si>
@@ -425,9 +468,6 @@
     <t>october-tourney-announcement</t>
   </si>
   <si>
-    <t>Save the Date: October 10th High-Stakes Tournamet</t>
-  </si>
-  <si>
     <t>I will be hosting a $50 buy-in tournament on October 10th at 6:30 PM. Please RSVP via Partiful. If you'd like an invite, shoot me a message.</t>
   </si>
   <si>
@@ -443,46 +483,31 @@
     <t>march-tourney-note</t>
   </si>
   <si>
-    <t>8 PM</t>
-  </si>
-  <si>
-    <t>cash-game-2026-08-15</t>
-  </si>
-  <si>
-    <t>Calvin A.</t>
-  </si>
-  <si>
-    <t>David B.</t>
-  </si>
-  <si>
-    <t>Dimple P.</t>
-  </si>
-  <si>
-    <t>cash-game-2026-08-19</t>
-  </si>
-  <si>
-    <t>Wednesday 8/19/26</t>
-  </si>
-  <si>
-    <t>Saturday 8/15/26</t>
-  </si>
-  <si>
-    <t>cash-game-2026-08-22</t>
-  </si>
-  <si>
-    <t>Saturday 8/22/26</t>
-  </si>
-  <si>
-    <t>cash-game-2026-08-26</t>
-  </si>
-  <si>
-    <t>Wednesday 8/26/26</t>
-  </si>
-  <si>
-    <t>cash-game-2026-08-29</t>
-  </si>
-  <si>
-    <t>Saturday 8/29/26</t>
+    <t>BLIND SCHEDULES</t>
+  </si>
+  <si>
+    <t>Add one row per level, using the exact Tournament ID from the Tournaments sheet.</t>
+  </si>
+  <si>
+    <t>Duration can be minutes or short text. Leave both blind amounts blank for a break; decimal levels such as 4.5 are allowed.</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Small Blind</t>
+  </si>
+  <si>
+    <t>Big Blind</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>Save the Date: October 10th High-Stakes Tournament</t>
   </si>
 </sst>
 </file>
@@ -494,7 +519,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -564,8 +589,25 @@
       <color rgb="FF17231D"/>
       <name val="Aptos"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF243C34"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF66766F"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -637,8 +679,23 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF143F35"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEBE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -813,11 +870,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF69C977"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF69C977"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF69C977"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF69C977"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -984,14 +1056,14 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1024,18 +1096,27 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="29">
     <dxf>
       <font>
         <b/>
@@ -1052,7 +1133,7 @@
         <color rgb="FF475569"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFE5E7EB"/>
         </patternFill>
       </fill>
@@ -1073,7 +1154,7 @@
         <color rgb="FF475569"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFE5E7EB"/>
         </patternFill>
       </fill>
@@ -1168,6 +1249,16 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1248,16 +1339,6 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1282,6 +1363,35 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF17231D"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFE3EAE6"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1314,17 +1424,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="27">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1348,15 +1458,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D105" totalsRowShown="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D105" totalsRowShown="0" dataDxfId="17">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1387,6 +1497,19 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Event ID" dataDxfId="6"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Expires" dataDxfId="5"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Pinned" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="BlindSchedulesTable" displayName="BlindSchedulesTable" ref="A4:E38" totalsRowShown="0">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Tournament ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Level"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Duration"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Small Blind"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Big Blind"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1597,106 +1720,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="74" t="s">
+      <c r="A1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="76" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="74" t="s">
+      <c r="A2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="76" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="75" t="s">
+      <c r="H3" s="77" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="76" t="s">
+      <c r="D5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="F5" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="76" t="s">
+      <c r="G5" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="78" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1704,22 +1827,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="E6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="71" t="s">
+      <c r="G6" s="73" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1731,22 +1854,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="74" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1758,22 +1881,22 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="71" t="s">
+      <c r="G8" s="73" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
@@ -1785,22 +1908,22 @@
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="69" t="s">
+      <c r="E9" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="74" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1812,22 +1935,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="71" t="s">
+      <c r="G10" s="73" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -1839,22 +1962,22 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="74" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
@@ -1864,184 +1987,184 @@
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="73" t="s">
+      <c r="E14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="73" t="s">
+      <c r="F14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="73" t="s">
+      <c r="H14" s="75" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="70" t="s">
+      <c r="E15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="70" t="s">
+      <c r="F15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="70" t="s">
+      <c r="G15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="70" t="s">
+      <c r="H15" s="72" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="69" t="s">
+      <c r="A16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="69" t="s">
+      <c r="E16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="69" t="s">
+      <c r="F16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="69" t="s">
+      <c r="H16" s="71" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="70" t="s">
+      <c r="A17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="72" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="69" t="s">
+      <c r="A18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="69" t="s">
+      <c r="D18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="69" t="s">
+      <c r="E18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="69" t="s">
+      <c r="F18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="69" t="s">
+      <c r="G18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="69" t="s">
+      <c r="H18" s="71" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="70" t="s">
+      <c r="D19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="70" t="s">
+      <c r="E19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="70" t="s">
+      <c r="F19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="70" t="s">
+      <c r="G19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="70" t="s">
+      <c r="H19" s="72" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="69" t="s">
+      <c r="F20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="69" t="s">
+      <c r="G20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="69" t="s">
+      <c r="H20" s="71" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2094,89 +2217,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="77" t="s">
+      <c r="F1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="77" t="s">
+      <c r="H1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="77" t="s">
+      <c r="I1" s="79" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="D2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="78" t="s">
+      <c r="G2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="78" t="s">
+      <c r="H2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="80" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="81" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2341,7 +2464,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="27" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="22.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
@@ -2356,43 +2479,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
     </row>
     <row r="2" spans="1:9" ht="27" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
     </row>
     <row r="3" spans="1:9" ht="27" customHeight="1">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -3072,7 +3195,7 @@
         <v>36</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="C33" s="14">
         <v>40</v>
@@ -3118,7 +3241,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C35" s="14">
         <v>40</v>
@@ -3540,7 +3663,7 @@
         <v>44</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="C51" s="14">
         <v>50</v>
@@ -3584,7 +3707,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="C55" s="14">
         <v>50</v>
@@ -3638,7 +3761,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
     <col min="2" max="2" width="27" style="1" customWidth="1"/>
@@ -3654,95 +3777,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
-      <c r="A1" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="77" t="s">
-        <v>79</v>
+      <c r="A1" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="79" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="20" customHeight="1">
-      <c r="A2" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="I2" s="78" t="s">
-        <v>80</v>
+      <c r="A2" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="80" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20" customHeight="1">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="81" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>28</v>
@@ -3771,13 +3894,13 @@
     </row>
     <row r="5" spans="1:9" ht="20" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D5" s="26">
         <v>46218</v>
@@ -3789,7 +3912,7 @@
         <v>39</v>
       </c>
       <c r="G5" s="65" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="H5" s="61">
         <v>20</v>
@@ -3798,13 +3921,13 @@
     </row>
     <row r="6" spans="1:9" ht="20" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D6" s="35">
         <v>46221</v>
@@ -3825,13 +3948,13 @@
     </row>
     <row r="7" spans="1:9" ht="20" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D7" s="35">
         <v>46225</v>
@@ -3852,13 +3975,13 @@
     </row>
     <row r="8" spans="1:9" ht="20" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D8" s="35">
         <v>46232</v>
@@ -3879,13 +4002,13 @@
     </row>
     <row r="9" spans="1:9" ht="20" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D9" s="28">
         <v>46239</v>
@@ -3905,13 +4028,13 @@
     </row>
     <row r="10" spans="1:9" ht="20" customHeight="1">
       <c r="A10" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D10" s="28">
         <v>46242</v>
@@ -3931,13 +4054,13 @@
     </row>
     <row r="11" spans="1:9" ht="20" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D11" s="28">
         <v>46246</v>
@@ -3957,13 +4080,13 @@
     </row>
     <row r="12" spans="1:9" ht="20" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="D12" s="28">
         <v>46249</v>
@@ -3983,13 +4106,13 @@
     </row>
     <row r="13" spans="1:9" ht="20" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="D13" s="28">
         <v>46253</v>
@@ -4009,13 +4132,13 @@
     </row>
     <row r="14" spans="1:9" ht="20" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="D14" s="28">
         <v>46256</v>
@@ -4035,13 +4158,13 @@
     </row>
     <row r="15" spans="1:9" ht="20" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="D15" s="28">
         <v>46260</v>
@@ -4061,13 +4184,13 @@
     </row>
     <row r="16" spans="1:9" ht="20" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="D16" s="28">
         <v>46263</v>
@@ -4116,7 +4239,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="23" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
@@ -4126,46 +4249,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23" customHeight="1">
-      <c r="A1" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="A1" s="82" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
     </row>
     <row r="2" spans="1:4" ht="23" customHeight="1">
-      <c r="A2" s="67" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
+      <c r="A2" s="84" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="23" customHeight="1">
-      <c r="A3" s="68" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
+      <c r="A3" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
     </row>
     <row r="4" spans="1:4" ht="23" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="23" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>46</v>
@@ -4179,7 +4302,7 @@
     </row>
     <row r="6" spans="1:4" ht="23" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>70</v>
@@ -4193,7 +4316,7 @@
     </row>
     <row r="7" spans="1:4" ht="23" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>62</v>
@@ -4207,7 +4330,7 @@
     </row>
     <row r="8" spans="1:4" ht="23" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>64</v>
@@ -4221,7 +4344,7 @@
     </row>
     <row r="9" spans="1:4" ht="23" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>63</v>
@@ -4235,7 +4358,7 @@
     </row>
     <row r="10" spans="1:4" ht="23" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>71</v>
@@ -4249,7 +4372,7 @@
     </row>
     <row r="11" spans="1:4" ht="23" customHeight="1">
       <c r="A11" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>38</v>
@@ -4263,7 +4386,7 @@
     </row>
     <row r="12" spans="1:4" ht="23" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>67</v>
@@ -4277,7 +4400,7 @@
     </row>
     <row r="13" spans="1:4" ht="23" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>68</v>
@@ -4291,7 +4414,7 @@
     </row>
     <row r="14" spans="1:4" ht="23" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>38</v>
@@ -4305,7 +4428,7 @@
     </row>
     <row r="15" spans="1:4" ht="23" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>70</v>
@@ -4319,10 +4442,10 @@
     </row>
     <row r="16" spans="1:4" ht="23" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" s="14">
         <v>50</v>
@@ -4333,7 +4456,7 @@
     </row>
     <row r="17" spans="1:4" ht="23" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>46</v>
@@ -4347,7 +4470,7 @@
     </row>
     <row r="18" spans="1:4" ht="23" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>71</v>
@@ -4361,7 +4484,7 @@
     </row>
     <row r="19" spans="1:4" ht="23" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>63</v>
@@ -4375,7 +4498,7 @@
     </row>
     <row r="20" spans="1:4" ht="23" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>62</v>
@@ -4389,7 +4512,7 @@
     </row>
     <row r="21" spans="1:4" ht="23" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>64</v>
@@ -4403,7 +4526,7 @@
     </row>
     <row r="22" spans="1:4" ht="23" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>46</v>
@@ -4417,7 +4540,7 @@
     </row>
     <row r="23" spans="1:4" ht="23" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>71</v>
@@ -4431,7 +4554,7 @@
     </row>
     <row r="24" spans="1:4" ht="23" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>63</v>
@@ -4445,7 +4568,7 @@
     </row>
     <row r="25" spans="1:4" ht="23" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>70</v>
@@ -4459,7 +4582,7 @@
     </row>
     <row r="26" spans="1:4" ht="23" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>67</v>
@@ -4473,7 +4596,7 @@
     </row>
     <row r="27" spans="1:4" ht="23" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>38</v>
@@ -4487,7 +4610,7 @@
     </row>
     <row r="28" spans="1:4" ht="23" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>68</v>
@@ -4501,7 +4624,7 @@
     </row>
     <row r="29" spans="1:4" ht="23" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>62</v>
@@ -4515,7 +4638,7 @@
     </row>
     <row r="30" spans="1:4" ht="23" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>64</v>
@@ -4529,7 +4652,7 @@
     </row>
     <row r="31" spans="1:4" ht="23" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>46</v>
@@ -4543,7 +4666,7 @@
     </row>
     <row r="32" spans="1:4" ht="23" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>70</v>
@@ -4557,7 +4680,7 @@
     </row>
     <row r="33" spans="1:4" ht="23" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>62</v>
@@ -4571,7 +4694,7 @@
     </row>
     <row r="34" spans="1:4" ht="23" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>64</v>
@@ -4585,7 +4708,7 @@
     </row>
     <row r="35" spans="1:4" ht="23" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>38</v>
@@ -4599,7 +4722,7 @@
     </row>
     <row r="36" spans="1:4" ht="23" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>63</v>
@@ -4613,7 +4736,7 @@
     </row>
     <row r="37" spans="1:4" ht="23" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>71</v>
@@ -4627,7 +4750,7 @@
     </row>
     <row r="38" spans="1:4" ht="23" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>68</v>
@@ -4641,7 +4764,7 @@
     </row>
     <row r="39" spans="1:4" ht="23" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>64</v>
@@ -4655,7 +4778,7 @@
     </row>
     <row r="40" spans="1:4" ht="23" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
@@ -4669,7 +4792,7 @@
     </row>
     <row r="41" spans="1:4" ht="23" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>46</v>
@@ -4683,10 +4806,10 @@
     </row>
     <row r="42" spans="1:4" ht="23" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C42" s="14">
         <v>20</v>
@@ -4697,7 +4820,7 @@
     </row>
     <row r="43" spans="1:4" ht="23" customHeight="1">
       <c r="A43" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>67</v>
@@ -4711,7 +4834,7 @@
     </row>
     <row r="44" spans="1:4" ht="23" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>70</v>
@@ -4725,7 +4848,7 @@
     </row>
     <row r="45" spans="1:4" ht="23" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>38</v>
@@ -4739,7 +4862,7 @@
     </row>
     <row r="46" spans="1:4" ht="23" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>71</v>
@@ -4753,7 +4876,7 @@
     </row>
     <row r="47" spans="1:4" ht="23" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>63</v>
@@ -4767,7 +4890,7 @@
     </row>
     <row r="48" spans="1:4" ht="23" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>59</v>
@@ -4781,7 +4904,7 @@
     </row>
     <row r="49" spans="1:4" ht="23" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>70</v>
@@ -4795,7 +4918,7 @@
     </row>
     <row r="50" spans="1:4" ht="23" customHeight="1">
       <c r="A50" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>67</v>
@@ -4809,7 +4932,7 @@
     </row>
     <row r="51" spans="1:4" ht="23" customHeight="1">
       <c r="A51" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>38</v>
@@ -4823,7 +4946,7 @@
     </row>
     <row r="52" spans="1:4" ht="23" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>71</v>
@@ -4837,7 +4960,7 @@
     </row>
     <row r="53" spans="1:4" ht="23" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>63</v>
@@ -4851,7 +4974,7 @@
     </row>
     <row r="54" spans="1:4" ht="23" customHeight="1">
       <c r="A54" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>64</v>
@@ -4865,7 +4988,7 @@
     </row>
     <row r="55" spans="1:4" ht="23" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>46</v>
@@ -4879,7 +5002,7 @@
     </row>
     <row r="56" spans="1:4" ht="23" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>62</v>
@@ -4893,7 +5016,7 @@
     </row>
     <row r="57" spans="1:4" ht="23" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>70</v>
@@ -4907,7 +5030,7 @@
     </row>
     <row r="58" spans="1:4" ht="23" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>71</v>
@@ -4921,7 +5044,7 @@
     </row>
     <row r="59" spans="1:4" ht="23" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>63</v>
@@ -4935,7 +5058,7 @@
     </row>
     <row r="60" spans="1:4" ht="23" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>38</v>
@@ -4949,7 +5072,7 @@
     </row>
     <row r="61" spans="1:4" ht="23" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>64</v>
@@ -4963,7 +5086,7 @@
     </row>
     <row r="62" spans="1:4" ht="23" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>62</v>
@@ -4977,10 +5100,10 @@
     </row>
     <row r="63" spans="1:4" ht="23" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C63" s="14">
         <v>20</v>
@@ -4991,7 +5114,7 @@
     </row>
     <row r="64" spans="1:4" ht="23" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>67</v>
@@ -5005,7 +5128,7 @@
     </row>
     <row r="65" spans="1:4" ht="23" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>46</v>
@@ -5019,7 +5142,7 @@
     </row>
     <row r="66" spans="1:4" ht="23" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>70</v>
@@ -5033,7 +5156,7 @@
     </row>
     <row r="67" spans="1:4" ht="23" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>71</v>
@@ -5047,7 +5170,7 @@
     </row>
     <row r="68" spans="1:4" ht="23" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>63</v>
@@ -5061,7 +5184,7 @@
     </row>
     <row r="69" spans="1:4" ht="23" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>68</v>
@@ -5075,10 +5198,10 @@
     </row>
     <row r="70" spans="1:4" ht="23" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C70" s="14">
         <v>20</v>
@@ -5089,7 +5212,7 @@
     </row>
     <row r="71" spans="1:4" ht="23" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>67</v>
@@ -5103,7 +5226,7 @@
     </row>
     <row r="72" spans="1:4" ht="23" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>62</v>
@@ -5117,7 +5240,7 @@
     </row>
     <row r="73" spans="1:4" ht="23" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>65</v>
@@ -5131,7 +5254,7 @@
     </row>
     <row r="74" spans="1:4" ht="23" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>64</v>
@@ -5145,7 +5268,7 @@
     </row>
     <row r="75" spans="1:4" ht="23" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>46</v>
@@ -5159,10 +5282,10 @@
     </row>
     <row r="76" spans="1:4" ht="23" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C76" s="14">
         <v>30</v>
@@ -5173,7 +5296,7 @@
     </row>
     <row r="77" spans="1:4" ht="23" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>62</v>
@@ -5187,7 +5310,7 @@
     </row>
     <row r="78" spans="1:4" ht="23" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>67</v>
@@ -5201,7 +5324,7 @@
     </row>
     <row r="79" spans="1:4" ht="23" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>70</v>
@@ -5215,7 +5338,7 @@
     </row>
     <row r="80" spans="1:4" ht="23" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>38</v>
@@ -5229,7 +5352,7 @@
     </row>
     <row r="81" spans="1:4" ht="23" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>71</v>
@@ -5243,7 +5366,7 @@
     </row>
     <row r="82" spans="1:4" ht="23" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>63</v>
@@ -5257,7 +5380,7 @@
     </row>
     <row r="83" spans="1:4" ht="23" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>68</v>
@@ -5271,7 +5394,7 @@
     </row>
     <row r="84" spans="1:4" ht="23" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>64</v>
@@ -5285,7 +5408,7 @@
     </row>
     <row r="85" spans="1:4" ht="23" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>71</v>
@@ -5299,7 +5422,7 @@
     </row>
     <row r="86" spans="1:4" ht="23" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>38</v>
@@ -5313,7 +5436,7 @@
     </row>
     <row r="87" spans="1:4" ht="23" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>65</v>
@@ -5327,7 +5450,7 @@
     </row>
     <row r="88" spans="1:4" ht="23" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>64</v>
@@ -5341,7 +5464,7 @@
     </row>
     <row r="89" spans="1:4" ht="23" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>70</v>
@@ -5355,7 +5478,7 @@
     </row>
     <row r="90" spans="1:4" ht="23" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>62</v>
@@ -5369,7 +5492,7 @@
     </row>
     <row r="91" spans="1:4" ht="23" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>63</v>
@@ -5383,7 +5506,7 @@
     </row>
     <row r="92" spans="1:4" ht="23" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>70</v>
@@ -5397,7 +5520,7 @@
     </row>
     <row r="93" spans="1:4" ht="23" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>38</v>
@@ -5411,7 +5534,7 @@
     </row>
     <row r="94" spans="1:4" ht="23" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
@@ -5425,7 +5548,7 @@
     </row>
     <row r="95" spans="1:4" ht="23" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>46</v>
@@ -5439,7 +5562,7 @@
     </row>
     <row r="96" spans="1:4" ht="23" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>67</v>
@@ -5453,7 +5576,7 @@
     </row>
     <row r="97" spans="1:4" ht="23" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>71</v>
@@ -5467,7 +5590,7 @@
     </row>
     <row r="98" spans="1:4" ht="23" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>64</v>
@@ -5481,7 +5604,7 @@
     </row>
     <row r="99" spans="1:4" ht="23" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>46</v>
@@ -5495,7 +5618,7 @@
     </row>
     <row r="100" spans="1:4" ht="23" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>70</v>
@@ -5509,7 +5632,7 @@
     </row>
     <row r="101" spans="1:4" ht="23" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>68</v>
@@ -5523,7 +5646,7 @@
     </row>
     <row r="102" spans="1:4" ht="23" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>38</v>
@@ -5537,7 +5660,7 @@
     </row>
     <row r="103" spans="1:4" ht="23" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>63</v>
@@ -5551,7 +5674,7 @@
     </row>
     <row r="104" spans="1:4" ht="23" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>71</v>
@@ -5565,7 +5688,7 @@
     </row>
     <row r="105" spans="1:4" ht="23" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>65</v>
@@ -5613,71 +5736,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="77" t="s">
-        <v>103</v>
+      <c r="A1" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="79" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="78" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="78" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="78" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="78" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="78" t="s">
-        <v>104</v>
+      <c r="A2" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="80" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="79" t="s">
-        <v>105</v>
+      <c r="A3" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="81" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17">
       <c r="A4" s="36" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30">
@@ -5685,13 +5808,13 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E5" s="38">
         <v>3</v>
@@ -5702,13 +5825,13 @@
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -5719,13 +5842,13 @@
         <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -5736,10 +5859,10 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -5780,77 +5903,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="77" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="77" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="77" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="77" t="s">
-        <v>120</v>
-      </c>
-      <c r="E1" s="77" t="s">
-        <v>120</v>
-      </c>
-      <c r="F1" s="77" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="77" t="s">
-        <v>120</v>
+      <c r="A1" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="79" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="G2" s="78" t="s">
-        <v>121</v>
+      <c r="A2" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" s="80" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="F3" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="79" t="s">
-        <v>122</v>
+      <c r="A3" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" s="81" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17">
       <c r="A4" s="36" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B4" s="36" t="s">
         <v>30</v>
@@ -5859,30 +5982,30 @@
         <v>29</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="51">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B5" s="58">
         <v>46243</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>44</v>
@@ -5891,21 +6014,21 @@
         <v>46305</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B6" s="59">
         <v>46236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>40</v>
@@ -5913,16 +6036,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B7" s="59">
         <v>46236</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>36</v>
@@ -5944,4 +6067,614 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="30" customHeight="1">
+      <c r="A1" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+    </row>
+    <row r="2" spans="1:5" ht="28" customHeight="1">
+      <c r="A2" s="69" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+    </row>
+    <row r="3" spans="1:5" ht="28" customHeight="1">
+      <c r="A3" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="66" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="66" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" s="66" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16">
+      <c r="A5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="66">
+        <v>1</v>
+      </c>
+      <c r="C5" s="66">
+        <v>20</v>
+      </c>
+      <c r="D5" s="67">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="67">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16">
+      <c r="A6" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>0.2</v>
+      </c>
+      <c r="E6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16">
+      <c r="A7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>0.3</v>
+      </c>
+      <c r="E7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16">
+      <c r="A8" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16">
+      <c r="A9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>0.4</v>
+      </c>
+      <c r="E9">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16">
+      <c r="A10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>0.5</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16">
+      <c r="A11" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16">
+      <c r="A12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>0.7</v>
+      </c>
+      <c r="E12">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16">
+      <c r="A13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>0.9</v>
+      </c>
+      <c r="E13">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16">
+      <c r="A14" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16">
+      <c r="A15" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>1.5</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16">
+      <c r="A16" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16">
+      <c r="A17" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17">
+        <v>11</v>
+      </c>
+      <c r="C17">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>2.5</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16">
+      <c r="A18" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16">
+      <c r="A19" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16">
+      <c r="A20" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>15</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16">
+      <c r="A21" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16">
+      <c r="A22" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>0.25</v>
+      </c>
+      <c r="E22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16">
+      <c r="A23" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <v>0.5</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16">
+      <c r="A24" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>0.75</v>
+      </c>
+      <c r="E24">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16">
+      <c r="A25" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16">
+      <c r="A26" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16">
+      <c r="A27" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>1.25</v>
+      </c>
+      <c r="E27">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="16">
+      <c r="A28" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+      <c r="C28">
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>1.5</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16">
+      <c r="A29" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16">
+      <c r="A30" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16">
+      <c r="A31" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>15</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16">
+      <c r="A32" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>15</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16">
+      <c r="A33" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33">
+        <v>15</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="16">
+      <c r="A34" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16">
+      <c r="A35" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35">
+        <v>11</v>
+      </c>
+      <c r="C35">
+        <v>15</v>
+      </c>
+      <c r="D35">
+        <v>6</v>
+      </c>
+      <c r="E35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16">
+      <c r="A36" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36">
+        <v>12</v>
+      </c>
+      <c r="C36">
+        <v>15</v>
+      </c>
+      <c r="D36">
+        <v>8</v>
+      </c>
+      <c r="E36">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16">
+      <c r="A37" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37">
+        <v>13</v>
+      </c>
+      <c r="C37">
+        <v>15</v>
+      </c>
+      <c r="D37">
+        <v>10</v>
+      </c>
+      <c r="E37">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16">
+      <c r="A38" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38">
+        <v>14</v>
+      </c>
+      <c r="C38">
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <v>12</v>
+      </c>
+      <c r="E38">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045395FB-741A-744E-9E6A-EC157686C7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0022C4EB-C89D-7040-AE3C-627C2E82FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="159">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -508,6 +508,15 @@
   </si>
   <si>
     <t>Save the Date: October 10th High-Stakes Tournament</t>
+  </si>
+  <si>
+    <t>cash-game-2026-09-02</t>
+  </si>
+  <si>
+    <t>Wednesday 9/2/26</t>
+  </si>
+  <si>
+    <t>Reid H.</t>
   </si>
 </sst>
 </file>
@@ -1441,7 +1450,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I16" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I17" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1458,7 +1467,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D105" totalsRowShown="0" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D117" totalsRowShown="0" dataDxfId="17">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1901,7 +1910,7 @@
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
@@ -1982,7 +1991,7 @@
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
@@ -3674,7 +3683,7 @@
         <v>44</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C52" s="14">
         <v>50</v>
@@ -3760,7 +3769,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -4208,6 +4217,32 @@
         <v>20</v>
       </c>
     </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="28">
+        <v>46267</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H17">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
@@ -4221,7 +4256,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="G5:G199 F5:F16" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="G5:G199 F5:F17" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4238,8 +4273,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:D117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
@@ -4248,7 +4283,7 @@
     <col min="5" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="23" customHeight="1">
+    <row r="1" spans="1:4" ht="25" customHeight="1">
       <c r="A1" s="82" t="s">
         <v>109</v>
       </c>
@@ -4256,7 +4291,7 @@
       <c r="C1" s="82"/>
       <c r="D1" s="82"/>
     </row>
-    <row r="2" spans="1:4" ht="23" customHeight="1">
+    <row r="2" spans="1:4" ht="25" customHeight="1">
       <c r="A2" s="84" t="s">
         <v>110</v>
       </c>
@@ -4264,7 +4299,7 @@
       <c r="C2" s="84"/>
       <c r="D2" s="84"/>
     </row>
-    <row r="3" spans="1:4" ht="23" customHeight="1">
+    <row r="3" spans="1:4" ht="25" customHeight="1">
       <c r="A3" s="87" t="s">
         <v>111</v>
       </c>
@@ -4272,7 +4307,7 @@
       <c r="C3" s="87"/>
       <c r="D3" s="87"/>
     </row>
-    <row r="4" spans="1:4" ht="23" customHeight="1">
+    <row r="4" spans="1:4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
@@ -4286,7 +4321,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="23" customHeight="1">
+    <row r="5" spans="1:4" ht="25" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>84</v>
       </c>
@@ -4300,7 +4335,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="23" customHeight="1">
+    <row r="6" spans="1:4" ht="25" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>84</v>
       </c>
@@ -4314,7 +4349,7 @@
         <v>41.25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="23" customHeight="1">
+    <row r="7" spans="1:4" ht="25" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>84</v>
       </c>
@@ -4328,7 +4363,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="23" customHeight="1">
+    <row r="8" spans="1:4" ht="25" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>84</v>
       </c>
@@ -4342,7 +4377,7 @@
         <v>48.55</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="23" customHeight="1">
+    <row r="9" spans="1:4" ht="25" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>84</v>
       </c>
@@ -4356,7 +4391,7 @@
         <v>23.25</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="23" customHeight="1">
+    <row r="10" spans="1:4" ht="25" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>84</v>
       </c>
@@ -4370,7 +4405,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="23" customHeight="1">
+    <row r="11" spans="1:4" ht="25" customHeight="1">
       <c r="A11" s="13" t="s">
         <v>84</v>
       </c>
@@ -4384,7 +4419,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="23" customHeight="1">
+    <row r="12" spans="1:4" ht="25" customHeight="1">
       <c r="A12" s="13" t="s">
         <v>84</v>
       </c>
@@ -4398,7 +4433,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="23" customHeight="1">
+    <row r="13" spans="1:4" ht="25" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>84</v>
       </c>
@@ -4412,7 +4447,7 @@
         <v>30.05</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="23" customHeight="1">
+    <row r="14" spans="1:4" ht="25" customHeight="1">
       <c r="A14" s="13" t="s">
         <v>87</v>
       </c>
@@ -4426,7 +4461,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="23" customHeight="1">
+    <row r="15" spans="1:4" ht="25" customHeight="1">
       <c r="A15" s="13" t="s">
         <v>87</v>
       </c>
@@ -4440,7 +4475,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="23" customHeight="1">
+    <row r="16" spans="1:4" ht="25" customHeight="1">
       <c r="A16" s="13" t="s">
         <v>87</v>
       </c>
@@ -4454,7 +4489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="23" customHeight="1">
+    <row r="17" spans="1:4" ht="25" customHeight="1">
       <c r="A17" s="13" t="s">
         <v>87</v>
       </c>
@@ -4468,7 +4503,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="23" customHeight="1">
+    <row r="18" spans="1:4" ht="25" customHeight="1">
       <c r="A18" s="13" t="s">
         <v>87</v>
       </c>
@@ -4482,7 +4517,7 @@
         <v>143.9</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="23" customHeight="1">
+    <row r="19" spans="1:4" ht="25" customHeight="1">
       <c r="A19" s="13" t="s">
         <v>87</v>
       </c>
@@ -4496,7 +4531,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="23" customHeight="1">
+    <row r="20" spans="1:4" ht="25" customHeight="1">
       <c r="A20" s="13" t="s">
         <v>87</v>
       </c>
@@ -4510,7 +4545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="23" customHeight="1">
+    <row r="21" spans="1:4" ht="25" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>87</v>
       </c>
@@ -4524,7 +4559,7 @@
         <v>148.9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="23" customHeight="1">
+    <row r="22" spans="1:4" ht="25" customHeight="1">
       <c r="A22" s="13" t="s">
         <v>89</v>
       </c>
@@ -4538,7 +4573,7 @@
         <v>73.75</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="23" customHeight="1">
+    <row r="23" spans="1:4" ht="25" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>89</v>
       </c>
@@ -4552,7 +4587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="23" customHeight="1">
+    <row r="24" spans="1:4" ht="25" customHeight="1">
       <c r="A24" s="13" t="s">
         <v>89</v>
       </c>
@@ -4566,7 +4601,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="23" customHeight="1">
+    <row r="25" spans="1:4" ht="25" customHeight="1">
       <c r="A25" s="13" t="s">
         <v>89</v>
       </c>
@@ -4580,7 +4615,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="23" customHeight="1">
+    <row r="26" spans="1:4" ht="25" customHeight="1">
       <c r="A26" s="13" t="s">
         <v>89</v>
       </c>
@@ -4594,7 +4629,7 @@
         <v>23.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="23" customHeight="1">
+    <row r="27" spans="1:4" ht="25" customHeight="1">
       <c r="A27" s="13" t="s">
         <v>89</v>
       </c>
@@ -4608,7 +4643,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="23" customHeight="1">
+    <row r="28" spans="1:4" ht="25" customHeight="1">
       <c r="A28" s="13" t="s">
         <v>89</v>
       </c>
@@ -4622,7 +4657,7 @@
         <v>30.25</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="23" customHeight="1">
+    <row r="29" spans="1:4" ht="25" customHeight="1">
       <c r="A29" s="13" t="s">
         <v>89</v>
       </c>
@@ -4636,7 +4671,7 @@
         <v>34.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="23" customHeight="1">
+    <row r="30" spans="1:4" ht="25" customHeight="1">
       <c r="A30" s="13" t="s">
         <v>89</v>
       </c>
@@ -4650,7 +4685,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="23" customHeight="1">
+    <row r="31" spans="1:4" ht="25" customHeight="1">
       <c r="A31" s="13" t="s">
         <v>91</v>
       </c>
@@ -4664,7 +4699,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="23" customHeight="1">
+    <row r="32" spans="1:4" ht="25" customHeight="1">
       <c r="A32" s="13" t="s">
         <v>91</v>
       </c>
@@ -4678,7 +4713,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="23" customHeight="1">
+    <row r="33" spans="1:4" ht="25" customHeight="1">
       <c r="A33" s="13" t="s">
         <v>91</v>
       </c>
@@ -4692,7 +4727,7 @@
         <v>47.75</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="23" customHeight="1">
+    <row r="34" spans="1:4" ht="25" customHeight="1">
       <c r="A34" s="13" t="s">
         <v>91</v>
       </c>
@@ -4706,7 +4741,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="23" customHeight="1">
+    <row r="35" spans="1:4" ht="25" customHeight="1">
       <c r="A35" s="13" t="s">
         <v>91</v>
       </c>
@@ -4720,7 +4755,7 @@
         <v>24.25</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="23" customHeight="1">
+    <row r="36" spans="1:4" ht="25" customHeight="1">
       <c r="A36" s="13" t="s">
         <v>91</v>
       </c>
@@ -4734,7 +4769,7 @@
         <v>48.25</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="23" customHeight="1">
+    <row r="37" spans="1:4" ht="25" customHeight="1">
       <c r="A37" s="13" t="s">
         <v>91</v>
       </c>
@@ -4748,7 +4783,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="23" customHeight="1">
+    <row r="38" spans="1:4" ht="25" customHeight="1">
       <c r="A38" s="13" t="s">
         <v>91</v>
       </c>
@@ -4762,7 +4797,7 @@
         <v>73.25</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="23" customHeight="1">
+    <row r="39" spans="1:4" ht="25" customHeight="1">
       <c r="A39" s="13" t="s">
         <v>93</v>
       </c>
@@ -4776,7 +4811,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="23" customHeight="1">
+    <row r="40" spans="1:4" ht="25" customHeight="1">
       <c r="A40" s="13" t="s">
         <v>93</v>
       </c>
@@ -4790,7 +4825,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="23" customHeight="1">
+    <row r="41" spans="1:4" ht="25" customHeight="1">
       <c r="A41" s="13" t="s">
         <v>93</v>
       </c>
@@ -4804,7 +4839,7 @@
         <v>29.25</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="23" customHeight="1">
+    <row r="42" spans="1:4" ht="25" customHeight="1">
       <c r="A42" s="13" t="s">
         <v>93</v>
       </c>
@@ -4818,7 +4853,7 @@
         <v>23.75</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="23" customHeight="1">
+    <row r="43" spans="1:4" ht="25" customHeight="1">
       <c r="A43" s="13" t="s">
         <v>93</v>
       </c>
@@ -4832,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="23" customHeight="1">
+    <row r="44" spans="1:4" ht="25" customHeight="1">
       <c r="A44" s="13" t="s">
         <v>93</v>
       </c>
@@ -4846,7 +4881,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="23" customHeight="1">
+    <row r="45" spans="1:4" ht="25" customHeight="1">
       <c r="A45" s="13" t="s">
         <v>93</v>
       </c>
@@ -4860,7 +4895,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="23" customHeight="1">
+    <row r="46" spans="1:4" ht="25" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>93</v>
       </c>
@@ -4874,7 +4909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="23" customHeight="1">
+    <row r="47" spans="1:4" ht="25" customHeight="1">
       <c r="A47" s="13" t="s">
         <v>93</v>
       </c>
@@ -4888,7 +4923,7 @@
         <v>73.75</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="23" customHeight="1">
+    <row r="48" spans="1:4" ht="25" customHeight="1">
       <c r="A48" s="13" t="s">
         <v>93</v>
       </c>
@@ -4902,7 +4937,7 @@
         <v>36.75</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="23" customHeight="1">
+    <row r="49" spans="1:4" ht="25" customHeight="1">
       <c r="A49" s="13" t="s">
         <v>95</v>
       </c>
@@ -4916,7 +4951,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="23" customHeight="1">
+    <row r="50" spans="1:4" ht="25" customHeight="1">
       <c r="A50" s="13" t="s">
         <v>95</v>
       </c>
@@ -4930,7 +4965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="23" customHeight="1">
+    <row r="51" spans="1:4" ht="25" customHeight="1">
       <c r="A51" s="13" t="s">
         <v>95</v>
       </c>
@@ -4944,7 +4979,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="23" customHeight="1">
+    <row r="52" spans="1:4" ht="25" customHeight="1">
       <c r="A52" s="13" t="s">
         <v>95</v>
       </c>
@@ -4958,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="23" customHeight="1">
+    <row r="53" spans="1:4" ht="25" customHeight="1">
       <c r="A53" s="13" t="s">
         <v>95</v>
       </c>
@@ -4972,7 +5007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="23" customHeight="1">
+    <row r="54" spans="1:4" ht="25" customHeight="1">
       <c r="A54" s="13" t="s">
         <v>95</v>
       </c>
@@ -4986,7 +5021,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="23" customHeight="1">
+    <row r="55" spans="1:4" ht="25" customHeight="1">
       <c r="A55" s="13" t="s">
         <v>95</v>
       </c>
@@ -5000,7 +5035,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="23" customHeight="1">
+    <row r="56" spans="1:4" ht="25" customHeight="1">
       <c r="A56" s="13" t="s">
         <v>95</v>
       </c>
@@ -5014,7 +5049,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="23" customHeight="1">
+    <row r="57" spans="1:4" ht="25" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>97</v>
       </c>
@@ -5028,7 +5063,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="23" customHeight="1">
+    <row r="58" spans="1:4" ht="25" customHeight="1">
       <c r="A58" s="1" t="s">
         <v>97</v>
       </c>
@@ -5042,7 +5077,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="23" customHeight="1">
+    <row r="59" spans="1:4" ht="25" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>97</v>
       </c>
@@ -5056,7 +5091,7 @@
         <v>37.700000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="23" customHeight="1">
+    <row r="60" spans="1:4" ht="25" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>97</v>
       </c>
@@ -5070,7 +5105,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="23" customHeight="1">
+    <row r="61" spans="1:4" ht="25" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>97</v>
       </c>
@@ -5084,7 +5119,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="23" customHeight="1">
+    <row r="62" spans="1:4" ht="25" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>97</v>
       </c>
@@ -5098,7 +5133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="23" customHeight="1">
+    <row r="63" spans="1:4" ht="25" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>97</v>
       </c>
@@ -5112,7 +5147,7 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="23" customHeight="1">
+    <row r="64" spans="1:4" ht="25" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>97</v>
       </c>
@@ -5126,7 +5161,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="23" customHeight="1">
+    <row r="65" spans="1:4" ht="25" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>99</v>
       </c>
@@ -5140,7 +5175,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="23" customHeight="1">
+    <row r="66" spans="1:4" ht="25" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>99</v>
       </c>
@@ -5154,7 +5189,7 @@
         <v>43.75</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="23" customHeight="1">
+    <row r="67" spans="1:4" ht="25" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>99</v>
       </c>
@@ -5168,7 +5203,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="23" customHeight="1">
+    <row r="68" spans="1:4" ht="25" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>99</v>
       </c>
@@ -5182,7 +5217,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="23" customHeight="1">
+    <row r="69" spans="1:4" ht="25" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>99</v>
       </c>
@@ -5196,7 +5231,7 @@
         <v>75.25</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="23" customHeight="1">
+    <row r="70" spans="1:4" ht="25" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>99</v>
       </c>
@@ -5210,7 +5245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="23" customHeight="1">
+    <row r="71" spans="1:4" ht="25" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>99</v>
       </c>
@@ -5224,7 +5259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="23" customHeight="1">
+    <row r="72" spans="1:4" ht="25" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>99</v>
       </c>
@@ -5238,7 +5273,7 @@
         <v>24.25</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="23" customHeight="1">
+    <row r="73" spans="1:4" ht="25" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>99</v>
       </c>
@@ -5252,7 +5287,7 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="23" customHeight="1">
+    <row r="74" spans="1:4" ht="25" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>99</v>
       </c>
@@ -5266,7 +5301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="23" customHeight="1">
+    <row r="75" spans="1:4" ht="25" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>101</v>
       </c>
@@ -5280,7 +5315,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="23" customHeight="1">
+    <row r="76" spans="1:4" ht="25" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>101</v>
       </c>
@@ -5294,7 +5329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="23" customHeight="1">
+    <row r="77" spans="1:4" ht="25" customHeight="1">
       <c r="A77" s="1" t="s">
         <v>101</v>
       </c>
@@ -5308,7 +5343,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="23" customHeight="1">
+    <row r="78" spans="1:4" ht="25" customHeight="1">
       <c r="A78" s="1" t="s">
         <v>101</v>
       </c>
@@ -5322,7 +5357,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="23" customHeight="1">
+    <row r="79" spans="1:4" ht="25" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>101</v>
       </c>
@@ -5336,7 +5371,7 @@
         <v>40.75</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="23" customHeight="1">
+    <row r="80" spans="1:4" ht="25" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>101</v>
       </c>
@@ -5350,7 +5385,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="23" customHeight="1">
+    <row r="81" spans="1:4" ht="25" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>101</v>
       </c>
@@ -5364,7 +5399,7 @@
         <v>81.25</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="23" customHeight="1">
+    <row r="82" spans="1:4" ht="25" customHeight="1">
       <c r="A82" s="1" t="s">
         <v>101</v>
       </c>
@@ -5378,7 +5413,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="23" customHeight="1">
+    <row r="83" spans="1:4" ht="25" customHeight="1">
       <c r="A83" s="1" t="s">
         <v>101</v>
       </c>
@@ -5392,7 +5427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="23" customHeight="1">
+    <row r="84" spans="1:4" ht="25" customHeight="1">
       <c r="A84" s="1" t="s">
         <v>101</v>
       </c>
@@ -5406,7 +5441,7 @@
         <v>25.25</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="23" customHeight="1">
+    <row r="85" spans="1:4" ht="25" customHeight="1">
       <c r="A85" s="1" t="s">
         <v>103</v>
       </c>
@@ -5420,7 +5455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="23" customHeight="1">
+    <row r="86" spans="1:4" ht="25" customHeight="1">
       <c r="A86" s="1" t="s">
         <v>103</v>
       </c>
@@ -5434,7 +5469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="23" customHeight="1">
+    <row r="87" spans="1:4" ht="25" customHeight="1">
       <c r="A87" s="1" t="s">
         <v>103</v>
       </c>
@@ -5448,7 +5483,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="23" customHeight="1">
+    <row r="88" spans="1:4" ht="25" customHeight="1">
       <c r="A88" s="1" t="s">
         <v>103</v>
       </c>
@@ -5462,7 +5497,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="23" customHeight="1">
+    <row r="89" spans="1:4" ht="25" customHeight="1">
       <c r="A89" s="1" t="s">
         <v>103</v>
       </c>
@@ -5476,7 +5511,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="23" customHeight="1">
+    <row r="90" spans="1:4" ht="25" customHeight="1">
       <c r="A90" s="1" t="s">
         <v>103</v>
       </c>
@@ -5490,7 +5525,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="23" customHeight="1">
+    <row r="91" spans="1:4" ht="25" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>103</v>
       </c>
@@ -5504,7 +5539,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="23" customHeight="1">
+    <row r="92" spans="1:4" ht="25" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>105</v>
       </c>
@@ -5518,7 +5553,7 @@
         <v>34.75</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="23" customHeight="1">
+    <row r="93" spans="1:4" ht="25" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>105</v>
       </c>
@@ -5532,7 +5567,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="23" customHeight="1">
+    <row r="94" spans="1:4" ht="25" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>105</v>
       </c>
@@ -5546,7 +5581,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="23" customHeight="1">
+    <row r="95" spans="1:4" ht="25" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>105</v>
       </c>
@@ -5560,7 +5595,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="23" customHeight="1">
+    <row r="96" spans="1:4" ht="25" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>105</v>
       </c>
@@ -5574,7 +5609,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="23" customHeight="1">
+    <row r="97" spans="1:4" ht="25" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>105</v>
       </c>
@@ -5588,7 +5623,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="23" customHeight="1">
+    <row r="98" spans="1:4" ht="25" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>105</v>
       </c>
@@ -5602,7 +5637,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="23" customHeight="1">
+    <row r="99" spans="1:4" ht="25" customHeight="1">
       <c r="A99" s="1" t="s">
         <v>107</v>
       </c>
@@ -5616,7 +5651,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="23" customHeight="1">
+    <row r="100" spans="1:4" ht="25" customHeight="1">
       <c r="A100" s="1" t="s">
         <v>107</v>
       </c>
@@ -5630,7 +5665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="23" customHeight="1">
+    <row r="101" spans="1:4" ht="25" customHeight="1">
       <c r="A101" s="1" t="s">
         <v>107</v>
       </c>
@@ -5644,7 +5679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="23" customHeight="1">
+    <row r="102" spans="1:4" ht="25" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>107</v>
       </c>
@@ -5658,7 +5693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="23" customHeight="1">
+    <row r="103" spans="1:4" ht="25" customHeight="1">
       <c r="A103" s="1" t="s">
         <v>107</v>
       </c>
@@ -5672,7 +5707,7 @@
         <v>104.1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="23" customHeight="1">
+    <row r="104" spans="1:4" ht="25" customHeight="1">
       <c r="A104" s="1" t="s">
         <v>107</v>
       </c>
@@ -5686,7 +5721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="23" customHeight="1">
+    <row r="105" spans="1:4" ht="25" customHeight="1">
       <c r="A105" s="1" t="s">
         <v>107</v>
       </c>
@@ -5698,6 +5733,174 @@
       </c>
       <c r="D105" s="14">
         <v>157.19999999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="25" customHeight="1">
+      <c r="A106" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C106" s="14">
+        <v>20</v>
+      </c>
+      <c r="D106" s="14">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="25" customHeight="1">
+      <c r="A107" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C107" s="14">
+        <v>40</v>
+      </c>
+      <c r="D107" s="14">
+        <v>26.75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="25" customHeight="1">
+      <c r="A108" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C108" s="14">
+        <v>30</v>
+      </c>
+      <c r="D108" s="14">
+        <v>61.25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="25" customHeight="1">
+      <c r="A109" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C109" s="14">
+        <v>20</v>
+      </c>
+      <c r="D109" s="14">
+        <v>73.75</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="25" customHeight="1">
+      <c r="A110" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C110" s="14">
+        <v>20</v>
+      </c>
+      <c r="D110" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="25" customHeight="1">
+      <c r="A111" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C111" s="14">
+        <v>20</v>
+      </c>
+      <c r="D111" s="14">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="25" customHeight="1">
+      <c r="A112" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C112" s="14">
+        <v>20</v>
+      </c>
+      <c r="D112" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="25" customHeight="1">
+      <c r="A113" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C113" s="14">
+        <v>20</v>
+      </c>
+      <c r="D113" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="25" customHeight="1">
+      <c r="A114" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C114" s="14">
+        <v>50</v>
+      </c>
+      <c r="D114" s="14">
+        <v>33.75</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="25" customHeight="1">
+      <c r="A115" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C115" s="14">
+        <v>20</v>
+      </c>
+      <c r="D115" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="25" customHeight="1">
+      <c r="A116" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116" s="14">
+        <v>40</v>
+      </c>
+      <c r="D116" s="14">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="25" customHeight="1">
+      <c r="A117" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C117" s="14">
+        <v>20</v>
+      </c>
+      <c r="D117" s="14">
+        <v>26.5</v>
       </c>
     </row>
   </sheetData>
